--- a/backend/data/Programas_UTEL_Todos_los_Paises.xlsx
+++ b/backend/data/Programas_UTEL_Todos_los_Paises.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="México" sheetId="1" r:id="Rec8a9fe19230405c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Argentina" sheetId="2" r:id="R22a659db91984d79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colombia" sheetId="3" r:id="R2ce759cbbbff44d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perú" sheetId="4" r:id="Rd81d7658f9334de7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ecuador" sheetId="5" r:id="R9e15cda776d34496"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USA" sheetId="6" r:id="Rd51c83df708f4d0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolivia" sheetId="7" r:id="R13859bb86dd24cfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chile" sheetId="8" r:id="R978704575c974064"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rep. Dominicana" sheetId="9" r:id="Rd64c061dbacf4b06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guatemala" sheetId="10" r:id="R6d992898185c4e5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panamá" sheetId="11" r:id="Rf079c04b3b7f4307"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="El Salvador" sheetId="12" r:id="R9d4ee99d510e466a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Philippines" sheetId="13" r:id="R00d5a821ecc640af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indonesia" sheetId="14" r:id="R89274043ad6b41e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paraguay" sheetId="15" r:id="Rc9fb697d9cab407a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="México" sheetId="1" r:id="Rc4bfb327b2a947d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Argentina" sheetId="2" r:id="R91e392f218c84c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colombia" sheetId="3" r:id="Raea4e128d6cd4aad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perú" sheetId="4" r:id="R5a870a95143c4a06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ecuador" sheetId="5" r:id="Rbfe0eb7a16bc478a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USA" sheetId="6" r:id="R533d04fc44644d25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolivia" sheetId="7" r:id="R39978a531c734051"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chile" sheetId="8" r:id="Rbe1f5296b4894665"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rep. Dominicana" sheetId="9" r:id="R31cafe523f98473a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guatemala" sheetId="10" r:id="R426808288b0c43f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panamá" sheetId="11" r:id="R43f9fa9f112444b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="El Salvador" sheetId="12" r:id="R9d95ec67dc0847ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Philippines" sheetId="13" r:id="Rfece84e4c547461d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indonesia" sheetId="14" r:id="Rfcbc542604c84129"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paraguay" sheetId="15" r:id="Rff9f671d4262411f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaMxico" displayName="TablaMxico" ref="A1:C201" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaMxico" displayName="TablaMxico" ref="A1:C202" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="NIVEL"/>
     <x:tableColumn id="2" name="PROGRAMA"/>
@@ -2832,10 +2832,21 @@
         <x:v>https://utel.edu.mx/bootcamp-fundamentos-de-desarrollo-web-proyectos-agiles-con-scrum</x:v>
       </x:c>
     </x:row>
+    <x:row r="202">
+      <x:c r="A202" t="str">
+        <x:v>Bachillerato</x:v>
+      </x:c>
+      <x:c r="B202" t="str">
+        <x:v>Bachillerato General</x:v>
+      </x:c>
+      <x:c r="C202" t="str">
+        <x:v>https://utel.edu.mx/bachillerato</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfba924d56f344a17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8baa7c2abab24ce4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3534,7 +3545,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b5e7b977d424a44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3ad489155c8486e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4112,7 +4123,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d7a3ec86ddf4f02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d5c65466f144dfd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4800,7 +4811,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f24145244304997"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a21d50d26164cdb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4982,7 +4993,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b7e7022c1af44f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57fd57160b37486d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5164,7 +5175,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a27a89bdc07466c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc54d273ae9754e53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5753,7 +5764,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd96c83e4127843c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90fd514441174b1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6540,7 +6551,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ad8ca28f1bd48fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb90d194695164906"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8594,7 +8605,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4dec1c2df564481"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd392a58bc314e50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10558,7 +10569,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b8b0002c44c44f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1f5d1b5deca417d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12243,7 +12254,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebc12711d9fd43b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfea8bdfef343402a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13433,7 +13444,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R103be5d0ae4049d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59ee5a0e19c44352"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14027,7 +14038,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bd900c4060149d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20d3683baad043d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14616,7 +14627,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a17905c7b3e49f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re47521aa312e46d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15846,7 +15857,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd72f45ca10bf472a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38664ed9076d4603"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/backend/data/Programas_UTEL_Todos_los_Paises.xlsx
+++ b/backend/data/Programas_UTEL_Todos_los_Paises.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="México" sheetId="1" r:id="Rc4bfb327b2a947d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Argentina" sheetId="2" r:id="R91e392f218c84c98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colombia" sheetId="3" r:id="Raea4e128d6cd4aad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perú" sheetId="4" r:id="R5a870a95143c4a06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ecuador" sheetId="5" r:id="Rbfe0eb7a16bc478a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USA" sheetId="6" r:id="R533d04fc44644d25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolivia" sheetId="7" r:id="R39978a531c734051"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chile" sheetId="8" r:id="Rbe1f5296b4894665"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rep. Dominicana" sheetId="9" r:id="R31cafe523f98473a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guatemala" sheetId="10" r:id="R426808288b0c43f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panamá" sheetId="11" r:id="R43f9fa9f112444b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="El Salvador" sheetId="12" r:id="R9d95ec67dc0847ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Philippines" sheetId="13" r:id="Rfece84e4c547461d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indonesia" sheetId="14" r:id="Rfcbc542604c84129"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paraguay" sheetId="15" r:id="Rff9f671d4262411f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="México" sheetId="1" r:id="Rab219a6509d24c97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Argentina" sheetId="2" r:id="Red616b0de2a6495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colombia" sheetId="3" r:id="R23087300d3524154"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perú" sheetId="4" r:id="Re75c73e4d40b4cf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ecuador" sheetId="5" r:id="R962a1485113644e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USA" sheetId="6" r:id="R401749cd67ff4d1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolivia" sheetId="7" r:id="R801c1c783ed04e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chile" sheetId="8" r:id="R0f130f586d9640fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rep. Dominicana" sheetId="9" r:id="R3c44cf035e344e91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guatemala" sheetId="10" r:id="R4492c4cd422d4573"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panamá" sheetId="11" r:id="R262bb3361dd3410f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="El Salvador" sheetId="12" r:id="Rc9291afbe741490a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Philippines" sheetId="13" r:id="R72dcbcf7842b4926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indonesia" sheetId="14" r:id="Rbec1ca992f5a4a9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paraguay" sheetId="15" r:id="Rc67221567fe349bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -39,7 +39,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -56,8 +56,28 @@
         <x:fgColor rgb="FFDDEBF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="24">
+  <x:borders count="48">
     <x:border/>
     <x:border/>
     <x:border/>
@@ -82,11 +102,70 @@
     <x:border/>
     <x:border/>
     <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:top/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:top/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:left/>
+    </x:border>
+    <x:border>
+      <x:right/>
+    </x:border>
+    <x:border>
+      <x:left/>
+    </x:border>
+    <x:border>
+      <x:right/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:bottom/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="62">
+  <x:cellXfs count="112">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -249,6 +328,154 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -257,7 +484,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaMxico" displayName="TablaMxico" ref="A1:C202" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="TablaMexicoCompleta" displayName="TablaMexicoCompleta" ref="A1:C407" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="NIVEL"/>
     <x:tableColumn id="2" name="PROGRAMA"/>
@@ -616,2237 +843,4492 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="64" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="66" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="88" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="10" t="str">
+      <x:c r="A1" s="90" t="str">
         <x:v>NIVEL</x:v>
       </x:c>
-      <x:c r="B1" s="11" t="str">
+      <x:c r="B1" s="91" t="str">
         <x:v>PROGRAMA</x:v>
       </x:c>
-      <x:c r="C1" s="12" t="str">
+      <x:c r="C1" s="92" t="str">
         <x:v>URL</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="44" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B2" s="45" t="str">
+      <x:c r="A2" s="106" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B2" s="107" t="str">
+        <x:v>Licenciatura en Ingeniería Industrial</x:v>
+      </x:c>
+      <x:c r="C2" s="108" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-industrial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B3" s="73" t="str">
+        <x:v>Licenciatura en Ingeniería Industrial y Administración</x:v>
+      </x:c>
+      <x:c r="C3" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-industrial-y-administracion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B4" s="110" t="str">
         <x:v>Licenciatura en Ingeniería en Sistemas Computacionales</x:v>
       </x:c>
-      <x:c r="C2" s="46" t="str">
+      <x:c r="C4" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-en-sistemas-computacionales</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B3" s="26" t="str">
+    <x:row r="5">
+      <x:c r="A5" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B5" s="73" t="str">
+        <x:v>Licenciatura en Administración de Recursos Humanos</x:v>
+      </x:c>
+      <x:c r="C5" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-recursos-humanos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B6" s="110" t="str">
+        <x:v>Licenciatura en Administración</x:v>
+      </x:c>
+      <x:c r="C6" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B7" s="73" t="str">
+        <x:v>Licenciatura en Administración y Finanzas</x:v>
+      </x:c>
+      <x:c r="C7" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion-y-finanzas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B8" s="110" t="str">
+        <x:v>Licenciatura en Administración de Negocios</x:v>
+      </x:c>
+      <x:c r="C8" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-negocios</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B9" s="73" t="str">
+        <x:v>Licenciatura en Administración de Tecnologías de la Información</x:v>
+      </x:c>
+      <x:c r="C9" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-tecnologias-de-informacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B10" s="110" t="str">
+        <x:v>Licenciatura en Contaduría Pública</x:v>
+      </x:c>
+      <x:c r="C10" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-contaduria-publica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B11" s="73" t="str">
+        <x:v>Licenciatura en Contaduría y Finanzas</x:v>
+      </x:c>
+      <x:c r="C11" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-contaduria-y-finanzas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B12" s="110" t="str">
+        <x:v>Licenciatura en Mercadotecnia</x:v>
+      </x:c>
+      <x:c r="C12" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-mercadotecnia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B13" s="73" t="str">
+        <x:v>Licenciatura en Negocios Internacionales</x:v>
+      </x:c>
+      <x:c r="C13" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-negocios-internacionales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B14" s="110" t="str">
+        <x:v>Licenciatura en Administración de Ventas</x:v>
+      </x:c>
+      <x:c r="C14" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-ventas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B15" s="73" t="str">
+        <x:v>Licenciatura en Economía y Finanzas</x:v>
+      </x:c>
+      <x:c r="C15" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-economia-y-finanzas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B16" s="110" t="str">
+        <x:v>Licenciatura en Comunicación Corporativa</x:v>
+      </x:c>
+      <x:c r="C16" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-comunicacion-corporativa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B17" s="73" t="str">
+        <x:v>Licenciatura en Medios Digitales</x:v>
+      </x:c>
+      <x:c r="C17" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-medios-digitales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B18" s="110" t="str">
+        <x:v>Licenciatura en Marketing y Publicidad</x:v>
+      </x:c>
+      <x:c r="C18" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-marketing-y-publicidad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B19" s="73" t="str">
+        <x:v>Licenciatura en Ciencias Políticas y Administración Pública</x:v>
+      </x:c>
+      <x:c r="C19" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-ciencias-politicas-y-administracion-publica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B20" s="110" t="str">
+        <x:v>Licenciatura en Criminología y Criminalística</x:v>
+      </x:c>
+      <x:c r="C20" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-criminologia-y-criminalistica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B21" s="73" t="str">
+        <x:v>Licenciatura en Comunicación Organizacional</x:v>
+      </x:c>
+      <x:c r="C21" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-comunicacion-organizacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B22" s="110" t="str">
+        <x:v>Licenciatura en Comunicación Digital</x:v>
+      </x:c>
+      <x:c r="C22" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-comunicacion-digital</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B23" s="73" t="str">
+        <x:v>Licenciatura en Comunicación</x:v>
+      </x:c>
+      <x:c r="C23" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-comunicacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B24" s="110" t="str">
+        <x:v>Licenciatura en Arte Digital y Multimedia</x:v>
+      </x:c>
+      <x:c r="C24" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-arte-digital-y-multimedia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B25" s="73" t="str">
+        <x:v>Licenciatura en Derecho Internacional</x:v>
+      </x:c>
+      <x:c r="C25" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-derecho-internacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B26" s="110" t="str">
+        <x:v>Licenciatura en Derecho Empresarial</x:v>
+      </x:c>
+      <x:c r="C26" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-derecho-empresarial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B27" s="73" t="str">
+        <x:v>Licenciatura en Derecho</x:v>
+      </x:c>
+      <x:c r="C27" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-derecho</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B28" s="110" t="str">
+        <x:v>Licenciatura en Psicología Organizacional</x:v>
+      </x:c>
+      <x:c r="C28" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-psicologia-organizacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B29" s="73" t="str">
+        <x:v>Licenciatura en Psicología</x:v>
+      </x:c>
+      <x:c r="C29" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-psicologia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B30" s="110" t="str">
+        <x:v>Licenciatura en Pedagogía</x:v>
+      </x:c>
+      <x:c r="C30" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-pedagogia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B31" s="73" t="str">
+        <x:v>Licenciatura en Tecnología Educativa</x:v>
+      </x:c>
+      <x:c r="C31" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-tecnologia-educativa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="109" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B32" s="110" t="str">
+        <x:v>Licenciatura en Administración de Empresas Turísticas</x:v>
+      </x:c>
+      <x:c r="C32" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-empresas-turisticas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="97" t="str">
+        <x:v>Licenciatura en línea</x:v>
+      </x:c>
+      <x:c r="B33" s="73" t="str">
+        <x:v>Licenciatura en Desarrollo Sustentable y Ecoturismo</x:v>
+      </x:c>
+      <x:c r="C33" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-desarrollo-sustentable-y-ecoturismo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B34" s="110" t="str">
+        <x:v>Maestría en Ciencia de Datos para Negocios</x:v>
+      </x:c>
+      <x:c r="C34" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-ciencia-de-datos-para-negocios</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B35" s="73" t="str">
+        <x:v>Maestría en Ciencias Computacionales y Telecomunicaciones</x:v>
+      </x:c>
+      <x:c r="C35" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-ciencias-computacionales-y-telecomunicaciones</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B36" s="110" t="str">
+        <x:v>Maestría en Ingeniería y Tecnología Ambiental</x:v>
+      </x:c>
+      <x:c r="C36" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-ingenieria-y-tecnologia-ambiental</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B37" s="73" t="str">
+        <x:v>Maestría en Dirección de Proyectos de Innovación</x:v>
+      </x:c>
+      <x:c r="C37" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-direccion-de-proyectos-de-innovacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B38" s="110" t="str">
+        <x:v>Maestría en Dirección e Ingeniería de Software</x:v>
+      </x:c>
+      <x:c r="C38" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-direccion-e-ingenieria-de-software</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B39" s="73" t="str">
+        <x:v>Maestría en Administración de Instituciones Educativas</x:v>
+      </x:c>
+      <x:c r="C39" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-de-instituciones-educativas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B40" s="110" t="str">
+        <x:v>Maestría en Administración en Mercadotecnia Estratégica</x:v>
+      </x:c>
+      <x:c r="C40" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-en-mercadotecnia-estrategica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B41" s="73" t="str">
+        <x:v>Maestría en Administración Pública</x:v>
+      </x:c>
+      <x:c r="C41" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-publica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B42" s="110" t="str">
+        <x:v>Maestría en Coaching Integral y Organizacional</x:v>
+      </x:c>
+      <x:c r="C42" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-coaching-integral-y-organizacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B43" s="73" t="str">
+        <x:v>Maestría en Comercio Internacional</x:v>
+      </x:c>
+      <x:c r="C43" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-comercio-internacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B44" s="110" t="str">
+        <x:v>Maestría en Dirección de Negocios de Alimentos y Bebidas</x:v>
+      </x:c>
+      <x:c r="C44" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-direccion-de-negocios-de-alimentos-y-bebidas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B45" s="73" t="str">
+        <x:v>Maestría en Dirección de Ventas</x:v>
+      </x:c>
+      <x:c r="C45" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-direccion-de-ventas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B46" s="110" t="str">
+        <x:v>Maestría en Gestión Organizacional Positiva</x:v>
+      </x:c>
+      <x:c r="C46" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-gestion-organizacional-positiva</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B47" s="73" t="str">
+        <x:v>MBA Internacional</x:v>
+      </x:c>
+      <x:c r="C47" s="98" t="str">
+        <x:v>https://utel.edu.mx/mba-internacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B48" s="110" t="str">
+        <x:v>Maestría en Administración de Negocios Deportivos</x:v>
+      </x:c>
+      <x:c r="C48" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-de-negocios-deportivos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B49" s="73" t="str">
+        <x:v>Maestría en Mercadotecnia Digital y Comercio Electrónico</x:v>
+      </x:c>
+      <x:c r="C49" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-mercadotecnia-digital-y-comercio-electronico</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B50" s="110" t="str">
+        <x:v>Maestría en Administración de Recursos Humanos</x:v>
+      </x:c>
+      <x:c r="C50" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-de-recursos-humanos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B51" s="73" t="str">
+        <x:v>Maestría en Administración de Tecnologías de la Información</x:v>
+      </x:c>
+      <x:c r="C51" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-de-tecnologias-de-la-informacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B52" s="110" t="str">
+        <x:v>Maestría en Gestión Estratégica del Capital Humano</x:v>
+      </x:c>
+      <x:c r="C52" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-gestion-estrategica-del-capital-humano</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B53" s="73" t="str">
+        <x:v>Maestría en Derecho Procesal Constitucional</x:v>
+      </x:c>
+      <x:c r="C53" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-derecho-procesal-constitucional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B54" s="110" t="str">
+        <x:v>Maestría en Derecho Procesal y Juicios Orales</x:v>
+      </x:c>
+      <x:c r="C54" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-derecho-procesal-y-juicios-orales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B55" s="73" t="str">
+        <x:v>Maestría en Educación y Docencia</x:v>
+      </x:c>
+      <x:c r="C55" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-educacion-y-docencia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B56" s="110" t="str">
+        <x:v>Maestría en Mindfulness (Conciencia Plena Aplicada)</x:v>
+      </x:c>
+      <x:c r="C56" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-conciencia-plena-aplicada</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B57" s="73" t="str">
+        <x:v>Maestría en Psicología Transpersonal</x:v>
+      </x:c>
+      <x:c r="C57" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-psicologia-transpersonal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B58" s="110" t="str">
+        <x:v>Maestría en Derecho Procesal Penal</x:v>
+      </x:c>
+      <x:c r="C58" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-derecho-procesal-penal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B59" s="73" t="str">
+        <x:v>Maestría en Tecnología Educativa</x:v>
+      </x:c>
+      <x:c r="C59" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-tecnologia-educativa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="109" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B60" s="110" t="str">
+        <x:v>Maestría en Gestión Directiva de Instituciones de Salud</x:v>
+      </x:c>
+      <x:c r="C60" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-gestion-directiva-de-instituciones-en-salud</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="97" t="str">
+        <x:v>Maestría en línea</x:v>
+      </x:c>
+      <x:c r="B61" s="73" t="str">
+        <x:v>Maestría en Dirección de Empresas Turísticas</x:v>
+      </x:c>
+      <x:c r="C61" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-direccion-de-empresas-turisticas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B62" s="110" t="str">
+        <x:v>Máster en Ciencias Computacionales y Telecomunicaciones</x:v>
+      </x:c>
+      <x:c r="C62" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-ciencias-computacionales-y-telecomunicaciones</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B63" s="73" t="str">
+        <x:v>Máster en Ciencia de Datos para Negocios</x:v>
+      </x:c>
+      <x:c r="C63" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-ciencia-de-datos-para-negocios</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B64" s="110" t="str">
+        <x:v>Máster en Dirección de Proyectos de Innovación</x:v>
+      </x:c>
+      <x:c r="C64" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-direccion-de-proyectos-de-innovacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B65" s="73" t="str">
+        <x:v>Máster en Ingeniería y Tecnología Ambiental</x:v>
+      </x:c>
+      <x:c r="C65" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-ingenieria-y-tecnologia-ambiental</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B66" s="110" t="str">
+        <x:v>Máster en Dirección e Ingeniería de Software</x:v>
+      </x:c>
+      <x:c r="C66" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-direccion-e-ingenieria-de-software</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B67" s="73" t="str">
+        <x:v>Máster en Ciberseguridad</x:v>
+      </x:c>
+      <x:c r="C67" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-ciber-seguridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B68" s="110" t="str">
+        <x:v>Máster en Energías Renovables y Eficiencia Energética</x:v>
+      </x:c>
+      <x:c r="C68" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-energias-renovables-y-eficiencia-energetica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B69" s="73" t="str">
+        <x:v>Máster en Logística y Cadena de Suministros</x:v>
+      </x:c>
+      <x:c r="C69" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-logistica-y-cadena-de-suministros</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B70" s="110" t="str">
+        <x:v>Maestría en Automatización de Procesos y Análisis Predictivo</x:v>
+      </x:c>
+      <x:c r="C70" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-automatizacion-de-procesos-y-analisis-predictivo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B71" s="73" t="str">
+        <x:v>Máster en Administración en Mercadotecnia Estratégica</x:v>
+      </x:c>
+      <x:c r="C71" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-administracion-en-mercadotecnia-estrategica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B72" s="110" t="str">
+        <x:v>Máster en Administración de Tecnologías de la Información</x:v>
+      </x:c>
+      <x:c r="C72" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-administracion-de-tecnologias-de-la-informacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B73" s="73" t="str">
+        <x:v>Máster en Administración Pública</x:v>
+      </x:c>
+      <x:c r="C73" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-administracion-publica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B74" s="110" t="str">
+        <x:v>Máster en Coaching Integral y Organizacional</x:v>
+      </x:c>
+      <x:c r="C74" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-coaching-integral-y-organizacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B75" s="73" t="str">
+        <x:v>Máster en Gestión Estratégica del Capital Humano</x:v>
+      </x:c>
+      <x:c r="C75" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-gestion-estrategica-del-capital-humano</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B76" s="110" t="str">
+        <x:v>Máster en Comercio Internacional</x:v>
+      </x:c>
+      <x:c r="C76" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-comercio-internacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B77" s="73" t="str">
+        <x:v>Máster en Dirección de Negocios de Alimentos y Bebidas</x:v>
+      </x:c>
+      <x:c r="C77" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-direccion-de-negocios-de-alimentos-y-bebidas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B78" s="110" t="str">
+        <x:v>Máster en Dirección de Ventas</x:v>
+      </x:c>
+      <x:c r="C78" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-direccion-de-ventas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B79" s="73" t="str">
+        <x:v>Máster en Finanzas</x:v>
+      </x:c>
+      <x:c r="C79" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-finanzas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B80" s="110" t="str">
+        <x:v>Máster en Gestión Organizacional Positiva</x:v>
+      </x:c>
+      <x:c r="C80" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-gestion-organizacional-positiva</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B81" s="73" t="str">
+        <x:v>Máster en Mercadotecnia Digital y Comercio Electrónico</x:v>
+      </x:c>
+      <x:c r="C81" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-mercadotecnia-digital-y-comercio-electronico</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B82" s="110" t="str">
+        <x:v>Máster en Impuestos</x:v>
+      </x:c>
+      <x:c r="C82" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-impuestos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B83" s="73" t="str">
+        <x:v>Máster en Administración de Negocios</x:v>
+      </x:c>
+      <x:c r="C83" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-administracion-de-negocios</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B84" s="110" t="str">
+        <x:v>Máster en Administración de Negocios Deportivos</x:v>
+      </x:c>
+      <x:c r="C84" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-administracion-de-negocios-deportivos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B85" s="73" t="str">
+        <x:v>Máster en Administración de Recursos Humanos</x:v>
+      </x:c>
+      <x:c r="C85" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-administracion-de-recursos-humanos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B86" s="110" t="str">
+        <x:v>Máster en Administración de Instituciones Educativas</x:v>
+      </x:c>
+      <x:c r="C86" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-administracion-de-instituciones-educativas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B87" s="73" t="str">
+        <x:v>Máster en Conciencia Plena Aplicada</x:v>
+      </x:c>
+      <x:c r="C87" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-conciencia-plena-aplicada</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B88" s="110" t="str">
+        <x:v>Máster en Derecho Procesal Penal</x:v>
+      </x:c>
+      <x:c r="C88" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-derecho-procesal-penal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B89" s="73" t="str">
+        <x:v>Máster en Educación y Docencia</x:v>
+      </x:c>
+      <x:c r="C89" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-educacion-y-docencia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B90" s="110" t="str">
+        <x:v>Máster en Derecho Procesal y Juicios Orales</x:v>
+      </x:c>
+      <x:c r="C90" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-derecho-procesal-y-juicios-orales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B91" s="73" t="str">
+        <x:v>Máster en Derecho Procesal Constitucional</x:v>
+      </x:c>
+      <x:c r="C91" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-derecho-procesal-constitucional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B92" s="110" t="str">
+        <x:v>Máster en Tecnología Educativa</x:v>
+      </x:c>
+      <x:c r="C92" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-tecnologia-educativa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B93" s="73" t="str">
+        <x:v>Máster en Derechos Humanos</x:v>
+      </x:c>
+      <x:c r="C93" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-derechos-humanos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B94" s="110" t="str">
+        <x:v>Máster en Desarrollo Sustentable y Gestión Ambiental</x:v>
+      </x:c>
+      <x:c r="C94" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-desarrollo-sustentable-y-gestion-ambiental</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B95" s="73" t="str">
+        <x:v>Máster en Diseño para Medios Digitales</x:v>
+      </x:c>
+      <x:c r="C95" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-diseno-para-medios-digitales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B96" s="110" t="str">
+        <x:v>Máster en Responsabilidad Social</x:v>
+      </x:c>
+      <x:c r="C96" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-responsabilidad-social</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B97" s="73" t="str">
+        <x:v>Máster en Mercadotecnia Política</x:v>
+      </x:c>
+      <x:c r="C97" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-mercadotecnia-politica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="109" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B98" s="110" t="str">
+        <x:v>Máster en Gestión Directiva de Instituciones en Salud</x:v>
+      </x:c>
+      <x:c r="C98" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-en-gestion-directiva-de-instituciones-en-salud</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="97" t="str">
+        <x:v>Máster en línea</x:v>
+      </x:c>
+      <x:c r="B99" s="73" t="str">
+        <x:v>Máster en Dirección de Empresas Turísticas</x:v>
+      </x:c>
+      <x:c r="C99" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-en-direccion-de-empresas-turisticas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="109" t="str">
+        <x:v>Máster Internacional en línea</x:v>
+      </x:c>
+      <x:c r="B100" s="110" t="str">
+        <x:v>Máster Internacional en Soluciones Avanzadas en Ciberseguridad</x:v>
+      </x:c>
+      <x:c r="C100" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-internacional-en-soluciones-avanzadas-en-ciberseguridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="97" t="str">
+        <x:v>Máster Internacional en línea</x:v>
+      </x:c>
+      <x:c r="B101" s="73" t="str">
+        <x:v>Máster Internacional en Desarrollo de Software y Estructuras de Datos</x:v>
+      </x:c>
+      <x:c r="C101" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-internacional-en-desarrollo-de-software-y-estructura-de-datos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="109" t="str">
+        <x:v>Máster Internacional en línea</x:v>
+      </x:c>
+      <x:c r="B102" s="110" t="str">
+        <x:v>Máster Internacional en Machine Learning</x:v>
+      </x:c>
+      <x:c r="C102" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-internacional-en-machine-learning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="97" t="str">
+        <x:v>Máster Internacional en línea</x:v>
+      </x:c>
+      <x:c r="B103" s="73" t="str">
+        <x:v>Máster Internacional en Ciencia de Datos</x:v>
+      </x:c>
+      <x:c r="C103" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-internacional-en-ciencia-de-datos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="109" t="str">
+        <x:v>Máster Internacional en línea</x:v>
+      </x:c>
+      <x:c r="B104" s="110" t="str">
+        <x:v>Máster Internacional en Análisis de Datos</x:v>
+      </x:c>
+      <x:c r="C104" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-internacional-en-analisis-de-datos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="97" t="str">
+        <x:v>Máster Internacional en línea</x:v>
+      </x:c>
+      <x:c r="B105" s="73" t="str">
+        <x:v>Máster Internacional en Dirección de Proyectos de Liderazgo</x:v>
+      </x:c>
+      <x:c r="C105" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-internacional-en-direccion-de-proyectos-de-liderazgo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="109" t="str">
+        <x:v>Máster Internacional en línea</x:v>
+      </x:c>
+      <x:c r="B106" s="110" t="str">
+        <x:v>Máster Internacional en Pensamiento Crítico para la Toma de Decisiones</x:v>
+      </x:c>
+      <x:c r="C106" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-internacional-en-pensamiento-critico-para-la-toma-de-decisiones</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="97" t="str">
+        <x:v>Máster Internacional en línea</x:v>
+      </x:c>
+      <x:c r="B107" s="73" t="str">
+        <x:v>Máster Internacional en Psicología de la Ansiedad, la Depresión y las Conductas Adictivas</x:v>
+      </x:c>
+      <x:c r="C107" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-internacional-en-psicologia-de-la-ansiedad-la-depresion-y-las-conductas-adictivas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="109" t="str">
+        <x:v>Máster Internacional en línea</x:v>
+      </x:c>
+      <x:c r="B108" s="110" t="str">
+        <x:v>Máster Internacional en Gestión en Hotelería y Turismo</x:v>
+      </x:c>
+      <x:c r="C108" s="111" t="str">
+        <x:v>https://utel.edu.mx/master-internacional-en-gestion-en-hoteleria-y-turismo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="97" t="str">
+        <x:v>Máster Internacional en línea</x:v>
+      </x:c>
+      <x:c r="B109" s="73" t="str">
+        <x:v>Máster Internacional en Neurociencia Médica</x:v>
+      </x:c>
+      <x:c r="C109" s="98" t="str">
+        <x:v>https://utel.edu.mx/master-internacional-en-neurociencia-medica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="109" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B110" s="110" t="str">
+        <x:v>Doctorado en Ciencia de Datos e Inteligencia Artificial</x:v>
+      </x:c>
+      <x:c r="C110" s="111" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-ciencia-de-datos-e-inteligencia-artificial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="97" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B111" s="73" t="str">
+        <x:v>Doctorado en Ciberseguridad de Sistemas Autónomos</x:v>
+      </x:c>
+      <x:c r="C111" s="98" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-ciberseguridad-de-sistemas-autonomos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="109" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B112" s="110" t="str">
+        <x:v>Doctorado en Ciberseguridad y Gestión de Riesgos Digitales</x:v>
+      </x:c>
+      <x:c r="C112" s="111" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-ciberseguridad-y-gestion-de-riesgos-digitales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="97" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B113" s="73" t="str">
+        <x:v>Doctorado en Administración Estratégica Empresarial</x:v>
+      </x:c>
+      <x:c r="C113" s="98" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-administracion-estrategica-empresarial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="109" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B114" s="110" t="str">
+        <x:v>Doctorado en Alta Dirección y Gobierno Corporativo</x:v>
+      </x:c>
+      <x:c r="C114" s="111" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-alta-direccion-y-gobierno-corporativo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="97" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B115" s="73" t="str">
+        <x:v>Doctorado en Gestión e Innovación Tecnológica</x:v>
+      </x:c>
+      <x:c r="C115" s="98" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-gestion-e-innovacion-tecnologica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="109" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B116" s="110" t="str">
+        <x:v>Doctorado en Educación</x:v>
+      </x:c>
+      <x:c r="C116" s="111" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-educacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="97" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B117" s="73" t="str">
+        <x:v>Doctorado en Tecnología Educativa e Innovación Didáctica</x:v>
+      </x:c>
+      <x:c r="C117" s="98" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-tecnologia-educativa-e-innovacion-didactica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="109" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B118" s="110" t="str">
+        <x:v>Doctorado en Evaluación de Políticas Sociales y Programas Públicos</x:v>
+      </x:c>
+      <x:c r="C118" s="111" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-evaluacion-de-politicas-sociales-y-programas-publicos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="97" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B119" s="73" t="str">
+        <x:v>Doctorado en Políticas Públicas y Gobernanza</x:v>
+      </x:c>
+      <x:c r="C119" s="98" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-politicas-publicas-y-gobernanza</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="109" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B120" s="110" t="str">
+        <x:v>Doctorado en Estudios Interculturales y Diversidad Humana</x:v>
+      </x:c>
+      <x:c r="C120" s="111" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-estudios-interculturales-y-diversidad-humana</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="97" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B121" s="73" t="str">
+        <x:v>Doctorado en Estudios Interdisciplinarios sobre América Latina</x:v>
+      </x:c>
+      <x:c r="C121" s="98" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-estudios-interdisciplinarios-sobre-america-latina</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="109" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B122" s="110" t="str">
+        <x:v>Doctorado en Liderazgo Educativo y Gestión Escolar</x:v>
+      </x:c>
+      <x:c r="C122" s="111" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-liderazgo-educativo-y-gestion-escolar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="97" t="str">
+        <x:v>Doctorado en línea</x:v>
+      </x:c>
+      <x:c r="B123" s="73" t="str">
+        <x:v>Doctorado en Desarrollo Humano</x:v>
+      </x:c>
+      <x:c r="C123" s="98" t="str">
+        <x:v>https://utel.edu.mx/doctorado-en-desarrollo-humano</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="109" t="str">
+        <x:v>Bachillerato en línea</x:v>
+      </x:c>
+      <x:c r="B124" s="110" t="str">
+        <x:v>Bachillerato General</x:v>
+      </x:c>
+      <x:c r="C124" s="111" t="str">
+        <x:v>https://utel.edu.mx/bachillerato</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B125" s="73" t="str">
+        <x:v>Diplomado en Project Management</x:v>
+      </x:c>
+      <x:c r="C125" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-project-management</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B126" s="110" t="str">
+        <x:v>Diplomado en Ciencias de Datos e Inteligencia Artificial</x:v>
+      </x:c>
+      <x:c r="C126" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-ciencias-de-datos-e-inteligencia-artificial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B127" s="73" t="str">
+        <x:v>Diplomado en Inteligencia Artificial Aplicada</x:v>
+      </x:c>
+      <x:c r="C127" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-inteligencia-artificial-aplicada</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B128" s="110" t="str">
+        <x:v>Diplomado en Diseño y Desarrollo de Software</x:v>
+      </x:c>
+      <x:c r="C128" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-diseno-y-desarrollo-de-software</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B129" s="73" t="str">
+        <x:v>Diplomado en Programación y Tecnología de Redes</x:v>
+      </x:c>
+      <x:c r="C129" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-programacion-y-tecnologia-de-redes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B130" s="110" t="str">
+        <x:v>Diplomado en Gestión de Calidad y Mantenimiento de Software</x:v>
+      </x:c>
+      <x:c r="C130" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-gestion-de-calidad-y-mantenimiento-de-software</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B131" s="73" t="str">
+        <x:v>Diplomado en Tecnologías de la Información Aplicadas a la Logística y el Transporte</x:v>
+      </x:c>
+      <x:c r="C131" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-tecnologias-de-la-informacion-aplicadas-a-la-logistica-y-el-transporte</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B132" s="110" t="str">
+        <x:v>Diplomado en Estrategias y Operaciones de Transporte</x:v>
+      </x:c>
+      <x:c r="C132" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-estrategias-y-operaciones-de-transporte</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B133" s="73" t="str">
+        <x:v>Diplomado en Animación Digital y Creación de Contenidos</x:v>
+      </x:c>
+      <x:c r="C133" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-animacion-digital-y-creacion-de-contenidos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B134" s="110" t="str">
+        <x:v>Diplomado en Desarrollo de Medios Interactivos</x:v>
+      </x:c>
+      <x:c r="C134" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-desarrollo-de-medios-interactivos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B135" s="73" t="str">
+        <x:v>Diplomado en Creatividad y Comunicación Digital</x:v>
+      </x:c>
+      <x:c r="C135" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-creatividad-y-comunicacion-digital</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B136" s="110" t="str">
+        <x:v>Diplomado en Fuentes y Tecnología de Energías Sostenibles</x:v>
+      </x:c>
+      <x:c r="C136" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-fuentes-y-tecnologia-de-energias-sostenibles</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B137" s="73" t="str">
+        <x:v>Diplomado en Gestión y Eficiencia de Sistemas Energéticos</x:v>
+      </x:c>
+      <x:c r="C137" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-gestion-y-eficiencia-de-sistemas-energeticos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B138" s="110" t="str">
+        <x:v>Diplomado en Transición Energética Sostenible</x:v>
+      </x:c>
+      <x:c r="C138" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-transicion-energetica-sostenible</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B139" s="73" t="str">
+        <x:v>Diplomado en Principios en el Arte Digital y Animación</x:v>
+      </x:c>
+      <x:c r="C139" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-principios-en-el-arte-digital-y-animacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B140" s="110" t="str">
+        <x:v>Diplomado en Desarrollo de E-learning</x:v>
+      </x:c>
+      <x:c r="C140" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-desarrollo-de-e-learning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B141" s="73" t="str">
+        <x:v>Diplomado en Administración de proyectos</x:v>
+      </x:c>
+      <x:c r="C141" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-administracion-de-proyectos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B142" s="110" t="str">
+        <x:v>Diplomado en Coaching Organizacional</x:v>
+      </x:c>
+      <x:c r="C142" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-coaching-organizacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B143" s="73" t="str">
+        <x:v>Diplomado en Administración Financiera</x:v>
+      </x:c>
+      <x:c r="C143" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-administracion-financiera</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B144" s="110" t="str">
+        <x:v>Diplomado en Dirección de Operaciones</x:v>
+      </x:c>
+      <x:c r="C144" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-direccion-de-operaciones</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B145" s="73" t="str">
+        <x:v>Diplomado en Administración de Servicios de Salud</x:v>
+      </x:c>
+      <x:c r="C145" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-administracion-de-servicios-de-salud</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B146" s="110" t="str">
+        <x:v>Diplomado en Contabilidad y Gestión Financiera</x:v>
+      </x:c>
+      <x:c r="C146" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-contabilidad-y-gestion-financiera</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B147" s="73" t="str">
+        <x:v>Diplomado en Estrategia e Innovación de Negocios</x:v>
+      </x:c>
+      <x:c r="C147" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-estrategia-e-innovacion-de-negocios</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B148" s="110" t="str">
+        <x:v>Diplomado en Análisis Económico Integral</x:v>
+      </x:c>
+      <x:c r="C148" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-analisis-Economico-integral</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B149" s="73" t="str">
+        <x:v>Diplomado en Métodos Cuantitativos para la Toma de Decisiones</x:v>
+      </x:c>
+      <x:c r="C149" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-metodos-cuantitativos-para-la-toma-de-decisiones</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B150" s="110" t="str">
+        <x:v>Diplomado en Habilidades digitales para el ambiente laboral</x:v>
+      </x:c>
+      <x:c r="C150" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-habilidades-digitales-para-el-ambiente-laboral</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B151" s="73" t="str">
+        <x:v>Diplomado en Pensamiento Crítico e Innovación</x:v>
+      </x:c>
+      <x:c r="C151" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-pensamiento-critico-e-innovacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B152" s="110" t="str">
+        <x:v>Diplomado en Soft skills y habilidades gerenciales</x:v>
+      </x:c>
+      <x:c r="C152" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-soft-skills-y-habilidades-gerenciales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B153" s="73" t="str">
+        <x:v>Diplomado en Tanatología</x:v>
+      </x:c>
+      <x:c r="C153" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-tanatologia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B154" s="110" t="str">
+        <x:v>Diplomado en Diversidad y Equidad de género</x:v>
+      </x:c>
+      <x:c r="C154" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-diversidad-y-equidad-de-genero</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B155" s="73" t="str">
+        <x:v>Diplomado en Diseño y Evaluación en Entornos Digitales</x:v>
+      </x:c>
+      <x:c r="C155" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-diseno-y-evaluacion-en-Entornos-digitales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B156" s="110" t="str">
+        <x:v>Diplomado en Gestión de Experiencias de Aprendizaje en Ambientes Virtuales</x:v>
+      </x:c>
+      <x:c r="C156" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-gestion-de-experiencias-de-aprendizaje-en-ambientes-virtuales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B157" s="73" t="str">
+        <x:v>Diplomado en Gestión Curricular en Educación a Distancia</x:v>
+      </x:c>
+      <x:c r="C157" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-gestion-curricular-en-educacion-a-distancia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B158" s="110" t="str">
+        <x:v>Diplomado en Atención al Adulto Mayor</x:v>
+      </x:c>
+      <x:c r="C158" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-atencion-al-adulto-mayor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B159" s="73" t="str">
+        <x:v>Diplomado en Nutrición Especial en Enfermedades Metabólicas</x:v>
+      </x:c>
+      <x:c r="C159" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-nutricion-especial-en-enfermedades-metabolicas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B160" s="110" t="str">
+        <x:v>Diplomado en Rehabilitación del Adulto Mayor</x:v>
+      </x:c>
+      <x:c r="C160" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-rehabilitacion-del-adulto-mayor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B161" s="73" t="str">
+        <x:v>Diplomado en Pruebas Psicológicas para Adultos</x:v>
+      </x:c>
+      <x:c r="C161" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-pruebas-psicologicas-para-adultos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B162" s="110" t="str">
+        <x:v>Diplomado en Mindfulness para los Individuos y las Familias</x:v>
+      </x:c>
+      <x:c r="C162" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-mindfulness-para-los-individuos-y-las-familias</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B163" s="73" t="str">
+        <x:v>Diplomado en Educación en Ciencias de la Salud</x:v>
+      </x:c>
+      <x:c r="C163" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-educacion-en-ciencias-de-la-salud</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="109" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B164" s="110" t="str">
+        <x:v>Diplomado en Actualización en Urgencias Médicas</x:v>
+      </x:c>
+      <x:c r="C164" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-actualizacion-en-urgencias-medicas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="97" t="str">
+        <x:v>Diplomado en línea</x:v>
+      </x:c>
+      <x:c r="B165" s="73" t="str">
+        <x:v>Diplomado en Actualización en Gineco-Obstetricia para el Primer y Segundo Nivel de Atención</x:v>
+      </x:c>
+      <x:c r="C165" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-en-actualizacion-en-gineco-obstetricia-para-el-primer-y-segundo-nivel-de-atencion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="109" t="str">
+        <x:v>Bootcamp en línea</x:v>
+      </x:c>
+      <x:c r="B166" s="110" t="str">
+        <x:v>Bootcamp Fundamentos de Python + Proyectos Ágiles con Scrum</x:v>
+      </x:c>
+      <x:c r="C166" s="111" t="str">
+        <x:v>https://utel.edu.mx/bootcamp-fundamentos-de-python-proyectos-agiles-con-scrum</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="97" t="str">
+        <x:v>Bootcamp en línea</x:v>
+      </x:c>
+      <x:c r="B167" s="73" t="str">
+        <x:v>Bootcamp Fundamentos de Ciencias de Datos + Proyectos Ágiles con Scrum</x:v>
+      </x:c>
+      <x:c r="C167" s="98" t="str">
+        <x:v>https://utel.edu.mx/bootcamp-fundamento-de-ciencias-de-datos-proyectos-agiles-con-scrum</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="109" t="str">
+        <x:v>Bootcamp en línea</x:v>
+      </x:c>
+      <x:c r="B168" s="110" t="str">
+        <x:v>Bootcamp Fundamentos de Desarrollo Web + Proyectos Ágiles con Scrum</x:v>
+      </x:c>
+      <x:c r="C168" s="111" t="str">
+        <x:v>https://utel.edu.mx/bootcamp-fundamentos-de-desarrollo-web-proyectos-agiles-con-scrum</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="97" t="str">
+        <x:v>Curso en línea</x:v>
+      </x:c>
+      <x:c r="B169" s="73" t="str">
+        <x:v>Curso de Inglés Evolve Digital (4 niveles)</x:v>
+      </x:c>
+      <x:c r="C169" s="98" t="str">
+        <x:v>https://utel.edu.mx/Idiomas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="109" t="str">
+        <x:v>Curso en línea</x:v>
+      </x:c>
+      <x:c r="B170" s="110" t="str">
+        <x:v>Curso Acredita-Bach</x:v>
+      </x:c>
+      <x:c r="C170" s="111" t="str">
+        <x:v>https://utel.edu.mx/bachillerato-acredita-bach</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B171" s="73" t="str">
+        <x:v>Licenciatura en Ingeniería en Sistemas Computacionales</x:v>
+      </x:c>
+      <x:c r="C171" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-en-sistemas-computacionales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B172" s="110" t="str">
         <x:v>Licenciatura en Ingeniería Industrial</x:v>
       </x:c>
-      <x:c r="C3" s="32" t="str">
+      <x:c r="C172" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-industrial</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B4" s="51" t="str">
+    <x:row r="173">
+      <x:c r="A173" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B173" s="73" t="str">
         <x:v>Licenciatura en Ingeniería Industrial y Administración</x:v>
       </x:c>
-      <x:c r="C4" s="52" t="str">
+      <x:c r="C173" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-industrial-y-administracion</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B5" s="26" t="str">
+    <x:row r="174">
+      <x:c r="A174" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B174" s="110" t="str">
         <x:v>Licenciatura en Ingeniería en Desarrollo de Software</x:v>
       </x:c>
-      <x:c r="C5" s="32" t="str">
+      <x:c r="C174" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-en-desarrollo-de-software</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B6" s="51" t="str">
+    <x:row r="175">
+      <x:c r="A175" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B175" s="73" t="str">
         <x:v>Licenciatura en Inteligencia Artificial</x:v>
       </x:c>
-      <x:c r="C6" s="52" t="str">
+      <x:c r="C175" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-inteligencia-artificial</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B7" s="26" t="str">
+    <x:row r="176">
+      <x:c r="A176" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B176" s="110" t="str">
         <x:v>Licenciatura en Seguridad Informática</x:v>
       </x:c>
-      <x:c r="C7" s="32" t="str">
+      <x:c r="C176" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-seguridad-informatica</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B8" s="51" t="str">
+    <x:row r="177">
+      <x:c r="A177" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B177" s="73" t="str">
         <x:v>Licenciatura en Tecnologías Interactivas y Virtuales</x:v>
       </x:c>
-      <x:c r="C8" s="52" t="str">
+      <x:c r="C177" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-tecnologias-interactivas-y-virtual</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B9" s="26" t="str">
+    <x:row r="178">
+      <x:c r="A178" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B178" s="110" t="str">
         <x:v>Licenciatura en Innovación y Emprendimiento con Inteligencia Artificial</x:v>
       </x:c>
-      <x:c r="C9" s="32" t="str">
+      <x:c r="C178" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-innovacion-y-emprendimiento-con-inteligencia-artificial</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B10" s="51" t="str">
+    <x:row r="179">
+      <x:c r="A179" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B179" s="73" t="str">
         <x:v>Licenciatura en Inteligencia Artificial Aplicada a Negocios, Industria y Automatización</x:v>
       </x:c>
-      <x:c r="C10" s="52" t="str">
+      <x:c r="C179" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-inteligencia-artificial-aplicada-a-negocios-industria-y-automatizacion</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B11" s="26" t="str">
+    <x:row r="180">
+      <x:c r="A180" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B180" s="110" t="str">
         <x:v>Licenciatura en Ingeniería en Tecnología de Videojuegos y Realidad Virtual</x:v>
       </x:c>
-      <x:c r="C11" s="32" t="str">
+      <x:c r="C180" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-en-tecnologia-de-videojuegos-y-realidad-virtual</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B12" s="51" t="str">
+    <x:row r="181">
+      <x:c r="A181" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B181" s="73" t="str">
         <x:v>Licenciatura en Ingeniería Robótica</x:v>
       </x:c>
-      <x:c r="C12" s="52" t="str">
+      <x:c r="C181" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-robotica</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B13" s="26" t="str">
+    <x:row r="182">
+      <x:c r="A182" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B182" s="110" t="str">
         <x:v>Licenciatura en Ética y Gobernanza de la Inteligencia Artificial</x:v>
       </x:c>
-      <x:c r="C13" s="32" t="str">
+      <x:c r="C182" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-etica-y-gobernanza-de-la-inteligencia-artificial</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B14" s="51" t="str">
+    <x:row r="183">
+      <x:c r="A183" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B183" s="73" t="str">
         <x:v>Licenciatura en Ingeniería en Ciencia de Datos e Inteligencia Analítica</x:v>
       </x:c>
-      <x:c r="C14" s="52" t="str">
+      <x:c r="C183" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-en-ciencia-de-datos-e-inteligencia-analitica</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B15" s="26" t="str">
+    <x:row r="184">
+      <x:c r="A184" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B184" s="110" t="str">
         <x:v>Licenciatura en Ingeniería en Programación en la Nube</x:v>
       </x:c>
-      <x:c r="C15" s="32" t="str">
+      <x:c r="C184" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-en-programacion-en-la-nube</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B16" s="51" t="str">
+    <x:row r="185">
+      <x:c r="A185" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B185" s="73" t="str">
         <x:v>Licenciatura en Ciberseguridad y Riesgos en Inteligencia Artificial</x:v>
       </x:c>
-      <x:c r="C16" s="52" t="str">
+      <x:c r="C185" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ciberseguridad-y-riesgos-en-inteligencia-artificial</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B17" s="26" t="str">
+    <x:row r="186">
+      <x:c r="A186" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B186" s="110" t="str">
         <x:v>Licenciatura en Ingeniería Ambiental</x:v>
       </x:c>
-      <x:c r="C17" s="32" t="str">
+      <x:c r="C186" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-ambiental</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B18" s="51" t="str">
+    <x:row r="187">
+      <x:c r="A187" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B187" s="73" t="str">
         <x:v>Licenciatura en Ingeniería en Sistemas Inteligentes</x:v>
       </x:c>
-      <x:c r="C18" s="52" t="str">
+      <x:c r="C187" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-en-sistemas-inteligentes</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B19" s="26" t="str">
+    <x:row r="188">
+      <x:c r="A188" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B188" s="110" t="str">
         <x:v>Licenciatura en Ingeniería en Energías Renovables</x:v>
       </x:c>
-      <x:c r="C19" s="32" t="str">
+      <x:c r="C188" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-en-energias-renovables</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B20" s="51" t="str">
+    <x:row r="189">
+      <x:c r="A189" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B189" s="73" t="str">
         <x:v>Licenciatura en Ingeniería en Logística y Transporte</x:v>
       </x:c>
-      <x:c r="C20" s="52" t="str">
+      <x:c r="C189" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-en-logistica-y-transporte</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B21" s="26" t="str">
+    <x:row r="190">
+      <x:c r="A190" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B190" s="110" t="str">
         <x:v>Licenciatura en Inteligencia Artificial y Ciencia de Datos</x:v>
       </x:c>
-      <x:c r="C21" s="32" t="str">
+      <x:c r="C190" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-inteligencia-artificial-y-ciencia-de-datos</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B22" s="51" t="str">
+    <x:row r="191">
+      <x:c r="A191" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B191" s="73" t="str">
         <x:v>Licenciatura en Software para Entretenimiento Digital</x:v>
       </x:c>
-      <x:c r="C22" s="52" t="str">
+      <x:c r="C191" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-software-para-entretenimiento-digital</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B23" s="26" t="str">
+    <x:row r="192">
+      <x:c r="A192" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B192" s="110" t="str">
         <x:v>Licenciatura en Diseño y Producción de Videojuegos</x:v>
       </x:c>
-      <x:c r="C23" s="32" t="str">
+      <x:c r="C192" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-diseno-y-produccion-de-videojuegos</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B24" s="51" t="str">
+    <x:row r="193">
+      <x:c r="A193" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B193" s="73" t="str">
         <x:v>Licenciatura en Ingeniería en Automatización Industrial</x:v>
       </x:c>
-      <x:c r="C24" s="52" t="str">
+      <x:c r="C193" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-en-automatizacion-industrial</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B25" s="26" t="str">
+    <x:row r="194">
+      <x:c r="A194" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B194" s="110" t="str">
         <x:v>Licenciatura en Tecnologías Interactivas y Experiencia e Interfaz de Usuario</x:v>
       </x:c>
-      <x:c r="C25" s="32" t="str">
+      <x:c r="C194" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-tecnologias-interactivas-y-experiencia-e-interfaz-de-usuario</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B26" s="51" t="str">
+    <x:row r="195">
+      <x:c r="A195" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B195" s="73" t="str">
         <x:v>Licenciatura en Administración y Finanzas</x:v>
       </x:c>
-      <x:c r="C26" s="52" t="str">
+      <x:c r="C195" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-administracion-y-finanzas</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B27" s="26" t="str">
+    <x:row r="196">
+      <x:c r="A196" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B196" s="110" t="str">
         <x:v>Licenciatura en Administración</x:v>
       </x:c>
-      <x:c r="C27" s="32" t="str">
+      <x:c r="C196" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-administracion</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B28" s="51" t="str">
+    <x:row r="197">
+      <x:c r="A197" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B197" s="73" t="str">
         <x:v>Licenciatura en Administración de Recursos Humanos</x:v>
       </x:c>
-      <x:c r="C28" s="52" t="str">
+      <x:c r="C197" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-recursos-humanos</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B29" s="26" t="str">
+    <x:row r="198">
+      <x:c r="A198" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B198" s="110" t="str">
         <x:v>Licenciatura en Administración de Tecnologías de Información</x:v>
       </x:c>
-      <x:c r="C29" s="32" t="str">
+      <x:c r="C198" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-tecnologias-de-informacion</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B30" s="51" t="str">
+    <x:row r="199">
+      <x:c r="A199" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B199" s="73" t="str">
         <x:v>Licenciatura en Contaduría Pública</x:v>
       </x:c>
-      <x:c r="C30" s="52" t="str">
+      <x:c r="C199" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-contaduria-publica</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B31" s="26" t="str">
+    <x:row r="200">
+      <x:c r="A200" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B200" s="110" t="str">
         <x:v>Licenciatura en Contaduría y Finanzas</x:v>
       </x:c>
-      <x:c r="C31" s="32" t="str">
+      <x:c r="C200" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-contaduria-y-finanzas</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B32" s="51" t="str">
+    <x:row r="201">
+      <x:c r="A201" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B201" s="73" t="str">
         <x:v>Licenciatura en Mercadotecnia</x:v>
       </x:c>
-      <x:c r="C32" s="52" t="str">
+      <x:c r="C201" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-mercadotecnia</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B33" s="26" t="str">
+    <x:row r="202">
+      <x:c r="A202" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B202" s="110" t="str">
         <x:v>Licenciatura en Negocios Internacionales</x:v>
       </x:c>
-      <x:c r="C33" s="32" t="str">
+      <x:c r="C202" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-negocios-internacionales</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B34" s="51" t="str">
+    <x:row r="203">
+      <x:c r="A203" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B203" s="73" t="str">
         <x:v>Licenciatura en Administración de Ventas</x:v>
       </x:c>
-      <x:c r="C34" s="52" t="str">
+      <x:c r="C203" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-ventas</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B35" s="26" t="str">
+    <x:row r="204">
+      <x:c r="A204" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B204" s="110" t="str">
         <x:v>Licenciatura en Economía y Finanzas</x:v>
       </x:c>
-      <x:c r="C35" s="32" t="str">
+      <x:c r="C204" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-economia-y-finanzas</x:v>
       </x:c>
     </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B36" s="51" t="str">
+    <x:row r="205">
+      <x:c r="A205" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B205" s="73" t="str">
         <x:v>Licenciatura en Agronegocios</x:v>
       </x:c>
-      <x:c r="C36" s="52" t="str">
+      <x:c r="C205" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-agronegocios</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B37" s="26" t="str">
+    <x:row r="206">
+      <x:c r="A206" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B206" s="110" t="str">
         <x:v>Licenciatura en Emprendimiento</x:v>
       </x:c>
-      <x:c r="C37" s="32" t="str">
+      <x:c r="C206" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-emprendimiento</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B38" s="51" t="str">
+    <x:row r="207">
+      <x:c r="A207" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B207" s="73" t="str">
         <x:v>Licenciatura en Finanzas y Banca</x:v>
       </x:c>
-      <x:c r="C38" s="52" t="str">
+      <x:c r="C207" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-finanzas-y-banca</x:v>
       </x:c>
     </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B39" s="26" t="str">
+    <x:row r="208">
+      <x:c r="A208" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B208" s="110" t="str">
         <x:v>Licenciatura en Finanzas y Estrategia Fiscal</x:v>
       </x:c>
-      <x:c r="C39" s="32" t="str">
+      <x:c r="C208" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-finanzas-y-estrategia-fiscal</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B40" s="51" t="str">
+    <x:row r="209">
+      <x:c r="A209" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B209" s="73" t="str">
         <x:v>Licenciatura en Administración de Empresas Turísticas</x:v>
       </x:c>
-      <x:c r="C40" s="52" t="str">
+      <x:c r="C209" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-empresas-turisticas</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B41" s="26" t="str">
+    <x:row r="210">
+      <x:c r="A210" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B210" s="110" t="str">
         <x:v>Licenciatura en Administración de Negocios</x:v>
       </x:c>
-      <x:c r="C41" s="32" t="str">
+      <x:c r="C210" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-negocios</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B42" s="51" t="str">
+    <x:row r="211">
+      <x:c r="A211" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B211" s="73" t="str">
         <x:v>Licenciatura en Comercio Electrónico y Negocios Digitales</x:v>
       </x:c>
-      <x:c r="C42" s="52" t="str">
+      <x:c r="C211" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-comercio-electronico-y-negocios-digitales</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B43" s="26" t="str">
+    <x:row r="212">
+      <x:c r="A212" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B212" s="110" t="str">
         <x:v>Licenciatura en Estrategia y Transformación de Negocios</x:v>
       </x:c>
-      <x:c r="C43" s="32" t="str">
+      <x:c r="C212" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-estrategia-y-transformacion-de-negocios</x:v>
       </x:c>
     </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B44" s="51" t="str">
+    <x:row r="213">
+      <x:c r="A213" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B213" s="73" t="str">
         <x:v>Licenciatura en Innovación y Transformación de Negocios</x:v>
       </x:c>
-      <x:c r="C44" s="52" t="str">
+      <x:c r="C213" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-innovacion-y-transformacion-de-negocios</x:v>
       </x:c>
     </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B45" s="26" t="str">
+    <x:row r="214">
+      <x:c r="A214" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B214" s="110" t="str">
         <x:v>Licenciatura en Marketing y Publicidad</x:v>
       </x:c>
-      <x:c r="C45" s="32" t="str">
+      <x:c r="C214" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-marketing-y-publicidad</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B46" s="51" t="str">
+    <x:row r="215">
+      <x:c r="A215" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B215" s="73" t="str">
         <x:v>Licenciatura en Medios Digitales</x:v>
       </x:c>
-      <x:c r="C46" s="52" t="str">
+      <x:c r="C215" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-medios-digitales</x:v>
       </x:c>
     </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B47" s="26" t="str">
+    <x:row r="216">
+      <x:c r="A216" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B216" s="110" t="str">
         <x:v>Licenciatura en Comercio Internacional</x:v>
       </x:c>
-      <x:c r="C47" s="32" t="str">
+      <x:c r="C216" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-comercio-internacional</x:v>
       </x:c>
     </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B48" s="51" t="str">
+    <x:row r="217">
+      <x:c r="A217" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B217" s="73" t="str">
         <x:v>Licenciatura en Comercialización y Dirección de Marcas</x:v>
       </x:c>
-      <x:c r="C48" s="52" t="str">
+      <x:c r="C217" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-comercializacion-y-direccion-de-marcas</x:v>
       </x:c>
     </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B49" s="26" t="str">
+    <x:row r="218">
+      <x:c r="A218" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B218" s="110" t="str">
         <x:v>Licenciatura en Consultoría y Desarrollo Empresarial</x:v>
       </x:c>
-      <x:c r="C49" s="32" t="str">
+      <x:c r="C218" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-consultoria-y-desarrollo-empresarial</x:v>
       </x:c>
     </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B50" s="51" t="str">
+    <x:row r="219">
+      <x:c r="A219" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B219" s="73" t="str">
         <x:v>Licenciatura en Publicidad y Medios</x:v>
       </x:c>
-      <x:c r="C50" s="52" t="str">
+      <x:c r="C219" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-publicidad-y-medios</x:v>
       </x:c>
     </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B51" s="26" t="str">
+    <x:row r="220">
+      <x:c r="A220" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B220" s="110" t="str">
         <x:v>Licenciatura en Administración de Negocios Gastronómicos</x:v>
       </x:c>
-      <x:c r="C51" s="32" t="str">
+      <x:c r="C220" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-negocios-gastronomicos</x:v>
       </x:c>
     </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B52" s="51" t="str">
+    <x:row r="221">
+      <x:c r="A221" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B221" s="73" t="str">
         <x:v>Licenciatura en Pedagogía</x:v>
       </x:c>
-      <x:c r="C52" s="52" t="str">
+      <x:c r="C221" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-pedagogia</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B53" s="26" t="str">
+    <x:row r="222">
+      <x:c r="A222" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B222" s="110" t="str">
         <x:v>Licenciatura en Tecnología Educativa</x:v>
       </x:c>
-      <x:c r="C53" s="32" t="str">
+      <x:c r="C222" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-tecnologia-educativa</x:v>
       </x:c>
     </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B54" s="51" t="str">
+    <x:row r="223">
+      <x:c r="A223" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B223" s="73" t="str">
         <x:v>Licenciatura en Educación para la Sustentabilidad</x:v>
       </x:c>
-      <x:c r="C54" s="52" t="str">
+      <x:c r="C223" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-educacion-para-la-sustentabilidad</x:v>
       </x:c>
     </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B55" s="26" t="str">
+    <x:row r="224">
+      <x:c r="A224" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B224" s="110" t="str">
         <x:v>Licenciatura en Desarrollo Sustentable y Ecoturismo</x:v>
       </x:c>
-      <x:c r="C55" s="32" t="str">
+      <x:c r="C224" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-desarrollo-sustentable-y-ecoturismo</x:v>
       </x:c>
     </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B56" s="51" t="str">
+    <x:row r="225">
+      <x:c r="A225" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B225" s="73" t="str">
         <x:v>Licenciatura en Inteligencia Artificial en Educación</x:v>
       </x:c>
-      <x:c r="C56" s="52" t="str">
+      <x:c r="C225" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-inteligencia-artificial-en-educacion</x:v>
       </x:c>
     </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B57" s="26" t="str">
+    <x:row r="226">
+      <x:c r="A226" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B226" s="110" t="str">
         <x:v>Licenciatura en Gestión de Políticas y Gobierno</x:v>
       </x:c>
-      <x:c r="C57" s="32" t="str">
+      <x:c r="C226" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-gestion-de-politicas-y-gobierno</x:v>
       </x:c>
     </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B58" s="51" t="str">
+    <x:row r="227">
+      <x:c r="A227" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B227" s="73" t="str">
         <x:v>Licenciatura en Seguridad Pública y Gobernabilidad Democrática</x:v>
       </x:c>
-      <x:c r="C58" s="52" t="str">
+      <x:c r="C227" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-seguridad-publica-y-gobernabilidad-democratica</x:v>
       </x:c>
     </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B59" s="26" t="str">
+    <x:row r="228">
+      <x:c r="A228" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B228" s="110" t="str">
         <x:v>Licenciatura en Lenguas Extranjeras</x:v>
       </x:c>
-      <x:c r="C59" s="32" t="str">
+      <x:c r="C228" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-lenguas-extranjeras</x:v>
       </x:c>
     </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B60" s="51" t="str">
+    <x:row r="229">
+      <x:c r="A229" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B229" s="73" t="str">
         <x:v>Licenciatura en Estudios Socioculturales</x:v>
       </x:c>
-      <x:c r="C60" s="52" t="str">
+      <x:c r="C229" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-estudios-socioculturales</x:v>
       </x:c>
     </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B61" s="26" t="str">
+    <x:row r="230">
+      <x:c r="A230" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B230" s="110" t="str">
         <x:v>Licenciatura en Lengua y Literatura</x:v>
       </x:c>
-      <x:c r="C61" s="32" t="str">
+      <x:c r="C230" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-lengua-y-literatura</x:v>
       </x:c>
     </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B62" s="51" t="str">
+    <x:row r="231">
+      <x:c r="A231" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B231" s="73" t="str">
         <x:v>Licenciatura en Antropología y Diversidad Cultural</x:v>
       </x:c>
-      <x:c r="C62" s="52" t="str">
+      <x:c r="C231" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-antropologia-y-diversidad-cultural</x:v>
       </x:c>
     </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B63" s="26" t="str">
+    <x:row r="232">
+      <x:c r="A232" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B232" s="110" t="str">
         <x:v>Licenciatura en Derechos Humanos y Justicia Social</x:v>
       </x:c>
-      <x:c r="C63" s="32" t="str">
+      <x:c r="C232" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-derechos-humanos-y-justicia-social</x:v>
       </x:c>
     </x:row>
-    <x:row r="64">
-      <x:c r="A64" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B64" s="51" t="str">
+    <x:row r="233">
+      <x:c r="A233" s="97" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B233" s="73" t="str">
         <x:v>Licenciatura en Psicología</x:v>
       </x:c>
-      <x:c r="C64" s="52" t="str">
+      <x:c r="C233" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-psicologia</x:v>
       </x:c>
     </x:row>
-    <x:row r="65">
-      <x:c r="A65" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B65" s="26" t="str">
+    <x:row r="234">
+      <x:c r="A234" s="109" t="str">
+        <x:v>Licenciatura Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B234" s="110" t="str">
         <x:v>Licenciatura en Psicología Organizacional</x:v>
       </x:c>
-      <x:c r="C65" s="32" t="str">
+      <x:c r="C234" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-psicologia-organizacional</x:v>
       </x:c>
     </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B66" s="51" t="str">
+    <x:row r="235">
+      <x:c r="A235" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B235" s="73" t="str">
+        <x:v>Maestría en Ciencia de Datos para Negocios</x:v>
+      </x:c>
+      <x:c r="C235" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-ciencia-de-datos-para-negocios</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B236" s="110" t="str">
+        <x:v>Maestría en Ingeniería y Tecnología Ambiental</x:v>
+      </x:c>
+      <x:c r="C236" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-ingenieria-y-tecnologia-ambiental</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B237" s="73" t="str">
+        <x:v>Maestría en Dirección e Ingeniería de Software</x:v>
+      </x:c>
+      <x:c r="C237" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-direccion-e-ingenieria-de-software</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B238" s="110" t="str">
+        <x:v>Maestría en Ciencias Computacionales y Telecomunicaciones</x:v>
+      </x:c>
+      <x:c r="C238" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-ciencias-computacionales-y-telecomunicaciones</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B239" s="73" t="str">
+        <x:v>Maestría en Ciberseguridad</x:v>
+      </x:c>
+      <x:c r="C239" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-ciberseguridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B240" s="110" t="str">
+        <x:v>Maestría en Innovación Estratégica con Inteligencia Artificial</x:v>
+      </x:c>
+      <x:c r="C240" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-innovacion-estrategica-con-inteligencia-artificial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B241" s="73" t="str">
+        <x:v>Maestría en Desarrollo de Videojuegos y Realidad Extendida</x:v>
+      </x:c>
+      <x:c r="C241" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-desarrollo-de-videojuegos-y-realidad-extendida</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B242" s="110" t="str">
+        <x:v>Maestría en Soluciones de Inteligencia Artificial para Negocios y Servicios</x:v>
+      </x:c>
+      <x:c r="C242" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-soluciones-de-inteligencia-artificial-para-negocios-y-servicios</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B243" s="73" t="str">
+        <x:v>Maestría en Automatización y Robótica Industrial</x:v>
+      </x:c>
+      <x:c r="C243" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-automatizacion-y-robotica-industrial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B244" s="110" t="str">
+        <x:v>Maestría en Arquitectura de Software</x:v>
+      </x:c>
+      <x:c r="C244" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-arquitectura-de-software</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B245" s="73" t="str">
+        <x:v>Maestría en Ingeniería de Datos e Infraestructura</x:v>
+      </x:c>
+      <x:c r="C245" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-ingenieria-de-datos-e-infraestructura</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B246" s="110" t="str">
+        <x:v>Maestría en Infraestructura y Cómputo en la Nube</x:v>
+      </x:c>
+      <x:c r="C246" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-infraestructura-y-computo-en-la-nube</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B247" s="73" t="str">
+        <x:v>Maestría en Interfaces Inteligentes y Tecnología Inmersiva</x:v>
+      </x:c>
+      <x:c r="C247" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-interfaces-inteligentes-y-tecnologia-inmersiva</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B248" s="110" t="str">
+        <x:v>Maestría en Gestión de la Calidad y Procesos Industriales</x:v>
+      </x:c>
+      <x:c r="C248" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-gestion-de-la-calidad-y-procesos-industriales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B249" s="73" t="str">
+        <x:v>Maestría en Evaluación de Riesgos Tecnológicos y Resiliencia Operativa</x:v>
+      </x:c>
+      <x:c r="C249" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-evaluacion-de-riesgos-tecnologicos-y-resiliencia-operativa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B250" s="110" t="str">
+        <x:v>Maestría en Gestión de Riesgos Ambientales</x:v>
+      </x:c>
+      <x:c r="C250" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-gestion-de-riesgos-ambientales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B251" s="73" t="str">
+        <x:v>MBA Internacional</x:v>
+      </x:c>
+      <x:c r="C251" s="98" t="str">
+        <x:v>https://utel.edu.mx/mba-internacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B252" s="110" t="str">
+        <x:v>Maestría en Administración de Negocios Deportivos</x:v>
+      </x:c>
+      <x:c r="C252" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-de-negocios-deportivos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B253" s="73" t="str">
+        <x:v>Maestría en Mercadotecnia Digital y Comercio Electrónico</x:v>
+      </x:c>
+      <x:c r="C253" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-mercadotecnia-digital-y-comercio-electronico</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B254" s="110" t="str">
+        <x:v>Maestría en Administración de Recursos Humanos</x:v>
+      </x:c>
+      <x:c r="C254" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-de-recursos-humanos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B255" s="73" t="str">
+        <x:v>Maestría en Administración de Tecnologías de la Información</x:v>
+      </x:c>
+      <x:c r="C255" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-de-tecnologias-de-la-informacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B256" s="110" t="str">
+        <x:v>Maestría en Dirección de Ventas</x:v>
+      </x:c>
+      <x:c r="C256" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-direccion-de-ventas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B257" s="73" t="str">
+        <x:v>Maestría en Administración en Mercadotecnia Estratégica</x:v>
+      </x:c>
+      <x:c r="C257" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-en-mercadotecnia-estrategica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B258" s="110" t="str">
+        <x:v>Maestría en Administración Pública</x:v>
+      </x:c>
+      <x:c r="C258" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-publica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B259" s="73" t="str">
+        <x:v>Maestría en Coaching Integral y Organizacional</x:v>
+      </x:c>
+      <x:c r="C259" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-coaching-integral-y-organizacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B260" s="110" t="str">
+        <x:v>Maestría en Comercio Internacional</x:v>
+      </x:c>
+      <x:c r="C260" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-comercio-internacional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B261" s="73" t="str">
+        <x:v>Maestría en Gestión Estratégica del Capital Humano</x:v>
+      </x:c>
+      <x:c r="C261" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-gestion-estrategica-del-capital-humano</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B262" s="110" t="str">
+        <x:v>Maestría en Gestión Organizacional Positiva</x:v>
+      </x:c>
+      <x:c r="C262" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-gestion-organizacional-positiva</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B263" s="73" t="str">
+        <x:v>Maestría en Finanzas</x:v>
+      </x:c>
+      <x:c r="C263" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-finanzas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B264" s="110" t="str">
+        <x:v>Maestría en Administración Pública con CIFAL Málaga y UNITAR</x:v>
+      </x:c>
+      <x:c r="C264" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-publica-con-cifal-malaga-y-unitar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B265" s="73" t="str">
+        <x:v>Maestría en Impuestos</x:v>
+      </x:c>
+      <x:c r="C265" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-impuestos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B266" s="110" t="str">
+        <x:v>Maestría en Administración de Instituciones Educativas</x:v>
+      </x:c>
+      <x:c r="C266" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-de-instituciones-educativas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B267" s="73" t="str">
+        <x:v>Maestría en Administración de Negocios</x:v>
+      </x:c>
+      <x:c r="C267" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-de-negocios</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B268" s="110" t="str">
+        <x:v>Maestría en Alta Dirección y Gobierno Corporativo</x:v>
+      </x:c>
+      <x:c r="C268" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-alta-direccion-y-gobierno-corporativo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B269" s="73" t="str">
+        <x:v>Maestría en Dirección de Proyectos de Innovación</x:v>
+      </x:c>
+      <x:c r="C269" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-direccion-de-proyectos-de-innovacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B270" s="110" t="str">
+        <x:v>Maestría en Gestión Directiva de Instituciones en Salud</x:v>
+      </x:c>
+      <x:c r="C270" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-gestion-directiva-de-instituciones-en-salud</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B271" s="73" t="str">
+        <x:v>Maestría en Logística y Cadena de Suministro</x:v>
+      </x:c>
+      <x:c r="C271" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-logistica-y-cadena-de-suministro</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B272" s="110" t="str">
+        <x:v>Maestría en Asesoría Empresarial Estratégica</x:v>
+      </x:c>
+      <x:c r="C272" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-asesoria-empresarial-estrategica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B273" s="73" t="str">
+        <x:v>Maestría en Inteligencia Financiera y Detección de Fraudes</x:v>
+      </x:c>
+      <x:c r="C273" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-inteligencia-financiera-y-deteccion-de-fraudes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B274" s="110" t="str">
+        <x:v>Maestría en Administración de Riesgos Financieros</x:v>
+      </x:c>
+      <x:c r="C274" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-administracion-de-riesgos-financieros</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B275" s="73" t="str">
+        <x:v>Maestría en Innovación en Modelos de Negocio</x:v>
+      </x:c>
+      <x:c r="C275" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-innovacion-en-modelos-de-negocio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B276" s="110" t="str">
+        <x:v>Maestría en Finanzas Sustentables y Proyectos de Inversión</x:v>
+      </x:c>
+      <x:c r="C276" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-finanzas-sustentables-y-proyectos-de-inversion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B277" s="73" t="str">
+        <x:v>Maestría en Economía Digital y Nuevas Formas de Mercado</x:v>
+      </x:c>
+      <x:c r="C277" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-economia-digital-y-nuevas-formas-de-mercado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B278" s="110" t="str">
+        <x:v>Maestría en Auditoría Financiera</x:v>
+      </x:c>
+      <x:c r="C278" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-auditoria-financiera</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B279" s="73" t="str">
+        <x:v>Maestría en Finanzas Públicas y Gestión Gubernamental</x:v>
+      </x:c>
+      <x:c r="C279" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-finanzas-publicas-y-gestion-gubernamental</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B280" s="110" t="str">
+        <x:v>Maestría en Economía Sustentable y Empresas Responsables</x:v>
+      </x:c>
+      <x:c r="C280" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-economia-sustentable-y-empresas-responsables</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B281" s="73" t="str">
+        <x:v>Maestría en Estrategias de Comercio Internacional y Aduanas</x:v>
+      </x:c>
+      <x:c r="C281" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-estrategias-de-comercio-internacional-y-aduanas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B282" s="110" t="str">
+        <x:v>Maestría en Cultura y Transformación Digital</x:v>
+      </x:c>
+      <x:c r="C282" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-cultura-y-transformacion-digital</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B283" s="73" t="str">
+        <x:v>Maestría en Educación y Docencia</x:v>
+      </x:c>
+      <x:c r="C283" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-educacion-y-docencia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B284" s="110" t="str">
+        <x:v>Maestría en Tecnología Educativa</x:v>
+      </x:c>
+      <x:c r="C284" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-tecnologia-educativa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B285" s="73" t="str">
+        <x:v>Maestría en Desarrollo Sustentable y Gestión Ambiental</x:v>
+      </x:c>
+      <x:c r="C285" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-desarrollo-sustentable-y-gestion-ambiental</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B286" s="110" t="str">
+        <x:v>Maestría en Responsabilidad Social</x:v>
+      </x:c>
+      <x:c r="C286" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-responsabilidad-social</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B287" s="73" t="str">
+        <x:v>Maestría en Innovación Educativa y Diseño Instruccional</x:v>
+      </x:c>
+      <x:c r="C287" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-innovacion-educativa-y-diseno-instruccional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B288" s="110" t="str">
+        <x:v>Maestría en Educación Inteligente y Diseño Instruccional con Inteligencia Artificial</x:v>
+      </x:c>
+      <x:c r="C288" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-educacion-inteligente-y-dise%C3%B1o-institucional-con-inteligencia-artificial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B289" s="73" t="str">
+        <x:v>Maestría en Energías Renovables y Eficiencia Energética</x:v>
+      </x:c>
+      <x:c r="C289" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-energias-renovables-y-eficiencia-energetica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B290" s="110" t="str">
+        <x:v>Maestría en Historia Pública y Educación Patrimonial</x:v>
+      </x:c>
+      <x:c r="C290" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-historia-publica-y-educacion-patrimonial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B291" s="73" t="str">
+        <x:v>Maestría en Análisis Político y Opinión Pública</x:v>
+      </x:c>
+      <x:c r="C291" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-analisis-politico-y-opinion-publica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B292" s="110" t="str">
+        <x:v>Maestría en Comunicación Social y Participación Ciudadana</x:v>
+      </x:c>
+      <x:c r="C292" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-comunicacion-social-y-participacion-ciudadana</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B293" s="73" t="str">
+        <x:v>Maestría en Políticas Sociales y Bienestar Social</x:v>
+      </x:c>
+      <x:c r="C293" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-politicas-sociales-y-bienestar-social</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B294" s="110" t="str">
+        <x:v>Maestría en Educación Inclusiva y Diversidad</x:v>
+      </x:c>
+      <x:c r="C294" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-educacion-inclusiva-y-diversidad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B295" s="73" t="str">
+        <x:v>Maestría en Filosofía y Pensamiento Crítico</x:v>
+      </x:c>
+      <x:c r="C295" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-filosofia-y-pensamiento-critico</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B296" s="110" t="str">
+        <x:v>Maestría en Justicia Social y Transformación Comunitaria</x:v>
+      </x:c>
+      <x:c r="C296" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-justicia-social-y-transformacion-comunitaria</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" s="101" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B297" s="79" t="str">
+        <x:v>Maestría en Mindfulness (Conciencia Plena Aplicada)</x:v>
+      </x:c>
+      <x:c r="C297" s="102" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-conciencia-plena-aplicada</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B298" s="110" t="str">
+        <x:v>Maestría en Psicología Transpersonal</x:v>
+      </x:c>
+      <x:c r="C298" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-psicologia-transpersonal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B299" s="73" t="str">
+        <x:v>Maestría en Dirección de Empresas Turísticas</x:v>
+      </x:c>
+      <x:c r="C299" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-direccion-de-empresas-turisticas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B300" s="110" t="str">
+        <x:v>Maestría en Dirección de Negocios de Alimentos y Bebidas</x:v>
+      </x:c>
+      <x:c r="C300" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-direccion-de-negocios-de-alimentos-y-bebidas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B301" s="73" t="str">
+        <x:v>Maestría en Turismo Digital y Gestión de Plataformas</x:v>
+      </x:c>
+      <x:c r="C301" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-turismo-digital-y-gestion-de-plataformas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302">
+      <x:c r="A302" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B302" s="110" t="str">
+        <x:v>Maestría en Dirección Estratégica de Hospitalidad y Bienestar</x:v>
+      </x:c>
+      <x:c r="C302" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-direccion-estrategica-de-hospitalidad-y-bienestar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303">
+      <x:c r="A303" s="97" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B303" s="73" t="str">
+        <x:v>Maestría en Organización de Eventos Corporativos y Convenciones</x:v>
+      </x:c>
+      <x:c r="C303" s="98" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-organizacion-de-eventos-corporativos-y-convenciones</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304">
+      <x:c r="A304" s="109" t="str">
+        <x:v>Maestría Ejecutiva</x:v>
+      </x:c>
+      <x:c r="B304" s="110" t="str">
+        <x:v>Maestría en Planeación Turística y Desarrollo Regional</x:v>
+      </x:c>
+      <x:c r="C304" s="111" t="str">
+        <x:v>https://utel.edu.mx/maestria-en-planeacion-turistica-y-desarrollo-regional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305">
+      <x:c r="A305" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B305" s="73" t="str">
+        <x:v>Licenciatura en Ingeniería en Sistemas Computacionales</x:v>
+      </x:c>
+      <x:c r="C305" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-en-sistemas-computacionales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306">
+      <x:c r="A306" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B306" s="110" t="str">
+        <x:v>Licenciatura en Ingeniería Industrial</x:v>
+      </x:c>
+      <x:c r="C306" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-industrial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307">
+      <x:c r="A307" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B307" s="73" t="str">
+        <x:v>Licenciatura en Ingeniería Industrial y Administración</x:v>
+      </x:c>
+      <x:c r="C307" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-ingenieria-industrial-y-administracion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308">
+      <x:c r="A308" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B308" s="110" t="str">
+        <x:v>Licenciatura en Administración y Finanzas</x:v>
+      </x:c>
+      <x:c r="C308" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion-y-finanzas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309">
+      <x:c r="A309" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B309" s="73" t="str">
+        <x:v>Licenciatura en Administración</x:v>
+      </x:c>
+      <x:c r="C309" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310">
+      <x:c r="A310" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B310" s="110" t="str">
+        <x:v>Licenciatura en Administración de Recursos Humanos</x:v>
+      </x:c>
+      <x:c r="C310" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-recursos-humanos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311">
+      <x:c r="A311" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B311" s="73" t="str">
+        <x:v>Licenciatura en Administración de Tecnologías de Información</x:v>
+      </x:c>
+      <x:c r="C311" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-tecnologias-de-informacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312">
+      <x:c r="A312" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B312" s="110" t="str">
+        <x:v>Licenciatura en Contaduría Pública</x:v>
+      </x:c>
+      <x:c r="C312" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-contaduria-publica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313">
+      <x:c r="A313" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B313" s="73" t="str">
+        <x:v>Licenciatura en Contaduría y Finanzas</x:v>
+      </x:c>
+      <x:c r="C313" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-contaduria-y-finanzas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314">
+      <x:c r="A314" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B314" s="110" t="str">
+        <x:v>Licenciatura en Mercadotecnia</x:v>
+      </x:c>
+      <x:c r="C314" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-mercadotecnia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315">
+      <x:c r="A315" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B315" s="73" t="str">
+        <x:v>Licenciatura en Negocios Internacionales</x:v>
+      </x:c>
+      <x:c r="C315" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-negocios-internacionales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316">
+      <x:c r="A316" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B316" s="110" t="str">
+        <x:v>Licenciatura en Administración de Ventas</x:v>
+      </x:c>
+      <x:c r="C316" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-ventas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317">
+      <x:c r="A317" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B317" s="73" t="str">
+        <x:v>Licenciatura en Economía y Finanzas</x:v>
+      </x:c>
+      <x:c r="C317" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-economia-y-finanzas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318">
+      <x:c r="A318" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B318" s="110" t="str">
         <x:v>Licenciatura en Comunicación Corporativa</x:v>
       </x:c>
-      <x:c r="C66" s="52" t="str">
+      <x:c r="C318" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-comunicacion-corporativa</x:v>
       </x:c>
     </x:row>
-    <x:row r="67">
-      <x:c r="A67" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B67" s="26" t="str">
+    <x:row r="319">
+      <x:c r="A319" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B319" s="73" t="str">
+        <x:v>Licenciatura en Medios Digitales</x:v>
+      </x:c>
+      <x:c r="C319" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-medios-digitales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320">
+      <x:c r="A320" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B320" s="110" t="str">
+        <x:v>Licenciatura en Marketing y Publicidad</x:v>
+      </x:c>
+      <x:c r="C320" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-marketing-y-publicidad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321">
+      <x:c r="A321" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B321" s="73" t="str">
         <x:v>Licenciatura en Ciencias Políticas y Administración Pública</x:v>
       </x:c>
-      <x:c r="C67" s="32" t="str">
+      <x:c r="C321" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-ciencias-politicas-y-administracion-publica</x:v>
       </x:c>
     </x:row>
-    <x:row r="68">
-      <x:c r="A68" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B68" s="51" t="str">
+    <x:row r="322">
+      <x:c r="A322" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B322" s="110" t="str">
         <x:v>Licenciatura en Criminología y Criminalística</x:v>
       </x:c>
-      <x:c r="C68" s="52" t="str">
+      <x:c r="C322" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-criminologia-y-criminalistica</x:v>
       </x:c>
     </x:row>
-    <x:row r="69">
-      <x:c r="A69" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B69" s="26" t="str">
+    <x:row r="323">
+      <x:c r="A323" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B323" s="73" t="str">
         <x:v>Licenciatura en Comunicación Organizacional</x:v>
       </x:c>
-      <x:c r="C69" s="32" t="str">
+      <x:c r="C323" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-comunicacion-organizacional</x:v>
       </x:c>
     </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B70" s="51" t="str">
+    <x:row r="324">
+      <x:c r="A324" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B324" s="110" t="str">
         <x:v>Licenciatura en Comunicación Digital</x:v>
       </x:c>
-      <x:c r="C70" s="52" t="str">
+      <x:c r="C324" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-comunicacion-digital</x:v>
       </x:c>
     </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B71" s="26" t="str">
+    <x:row r="325">
+      <x:c r="A325" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B325" s="73" t="str">
         <x:v>Licenciatura en Comunicación</x:v>
       </x:c>
-      <x:c r="C71" s="32" t="str">
+      <x:c r="C325" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-comunicacion</x:v>
       </x:c>
     </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="50" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B72" s="51" t="str">
+    <x:row r="326">
+      <x:c r="A326" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B326" s="110" t="str">
         <x:v>Licenciatura en Arte Digital y Multimedia</x:v>
       </x:c>
-      <x:c r="C72" s="52" t="str">
+      <x:c r="C326" s="111" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-arte-digital-y-multimedia</x:v>
       </x:c>
     </x:row>
-    <x:row r="73">
-      <x:c r="A73" s="31" t="str">
-        <x:v>Licenciatura</x:v>
-      </x:c>
-      <x:c r="B73" s="26" t="str">
+    <x:row r="327">
+      <x:c r="A327" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B327" s="73" t="str">
         <x:v>Licenciatura en Derecho Internacional</x:v>
       </x:c>
-      <x:c r="C73" s="32" t="str">
+      <x:c r="C327" s="98" t="str">
         <x:v>https://utel.edu.mx/licenciatura-en-derecho-internacional</x:v>
       </x:c>
     </x:row>
-    <x:row r="74">
-      <x:c r="A74" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B74" s="51" t="str">
+    <x:row r="328">
+      <x:c r="A328" s="109" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B328" s="110" t="str">
+        <x:v>Licenciatura en Administración de Empresas Turísticas</x:v>
+      </x:c>
+      <x:c r="C328" s="111" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-administracion-de-empresas-turisticas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329">
+      <x:c r="A329" s="97" t="str">
+        <x:v>Licenciatura Híbrida</x:v>
+      </x:c>
+      <x:c r="B329" s="73" t="str">
+        <x:v>Licenciatura en Desarrollo Sustentable y Ecoturismo</x:v>
+      </x:c>
+      <x:c r="C329" s="98" t="str">
+        <x:v>https://utel.edu.mx/licenciatura-en-desarrollo-sustentable-y-ecoturismo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330">
+      <x:c r="A330" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B330" s="110" t="str">
         <x:v>Maestría en Ciencia de Datos para Negocios</x:v>
       </x:c>
-      <x:c r="C74" s="52" t="str">
+      <x:c r="C330" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-ciencia-de-datos-para-negocios</x:v>
       </x:c>
     </x:row>
-    <x:row r="75">
-      <x:c r="A75" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B75" s="26" t="str">
+    <x:row r="331">
+      <x:c r="A331" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B331" s="73" t="str">
         <x:v>Maestría en Ingeniería y Tecnología Ambiental</x:v>
       </x:c>
-      <x:c r="C75" s="32" t="str">
+      <x:c r="C331" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-ingenieria-y-tecnologia-ambiental</x:v>
       </x:c>
     </x:row>
-    <x:row r="76">
-      <x:c r="A76" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B76" s="51" t="str">
+    <x:row r="332">
+      <x:c r="A332" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B332" s="110" t="str">
         <x:v>Maestría en Dirección e Ingeniería de Software</x:v>
       </x:c>
-      <x:c r="C76" s="52" t="str">
+      <x:c r="C332" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-direccion-e-ingenieria-de-software</x:v>
       </x:c>
     </x:row>
-    <x:row r="77">
-      <x:c r="A77" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B77" s="26" t="str">
+    <x:row r="333">
+      <x:c r="A333" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B333" s="73" t="str">
         <x:v>Maestría en Ciencias Computacionales y Telecomunicaciones</x:v>
       </x:c>
-      <x:c r="C77" s="32" t="str">
+      <x:c r="C333" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-ciencias-computacionales-y-telecomunicaciones</x:v>
       </x:c>
     </x:row>
-    <x:row r="78">
-      <x:c r="A78" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B78" s="51" t="str">
+    <x:row r="334">
+      <x:c r="A334" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B334" s="110" t="str">
         <x:v>Maestría en Ciberseguridad</x:v>
       </x:c>
-      <x:c r="C78" s="52" t="str">
+      <x:c r="C334" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-ciberseguridad</x:v>
       </x:c>
     </x:row>
-    <x:row r="79">
-      <x:c r="A79" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B79" s="26" t="str">
+    <x:row r="335">
+      <x:c r="A335" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B335" s="73" t="str">
         <x:v>Maestría en Innovación Estratégica con Inteligencia Artificial</x:v>
       </x:c>
-      <x:c r="C79" s="32" t="str">
+      <x:c r="C335" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-innovacion-estrategica-con-inteligencia-artificial</x:v>
       </x:c>
     </x:row>
-    <x:row r="80">
-      <x:c r="A80" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B80" s="51" t="str">
+    <x:row r="336">
+      <x:c r="A336" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B336" s="110" t="str">
         <x:v>Maestría en Desarrollo de Videojuegos y Realidad Extendida</x:v>
       </x:c>
-      <x:c r="C80" s="52" t="str">
+      <x:c r="C336" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-desarrollo-de-videojuegos-y-realidad-extendida</x:v>
       </x:c>
     </x:row>
-    <x:row r="81">
-      <x:c r="A81" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B81" s="26" t="str">
+    <x:row r="337">
+      <x:c r="A337" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B337" s="73" t="str">
         <x:v>Maestría en Soluciones de Inteligencia Artificial para Negocios y Servicios</x:v>
       </x:c>
-      <x:c r="C81" s="32" t="str">
+      <x:c r="C337" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-soluciones-de-inteligencia-artificial-para-negocios-y-servicios</x:v>
       </x:c>
     </x:row>
-    <x:row r="82">
-      <x:c r="A82" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B82" s="51" t="str">
+    <x:row r="338">
+      <x:c r="A338" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B338" s="110" t="str">
         <x:v>Maestría en Automatización y Robótica Industrial</x:v>
       </x:c>
-      <x:c r="C82" s="52" t="str">
+      <x:c r="C338" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-automatizacion-y-robotica-industrial</x:v>
       </x:c>
     </x:row>
-    <x:row r="83">
-      <x:c r="A83" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B83" s="26" t="str">
+    <x:row r="339">
+      <x:c r="A339" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B339" s="73" t="str">
         <x:v>Maestría en Arquitectura de Software</x:v>
       </x:c>
-      <x:c r="C83" s="32" t="str">
+      <x:c r="C339" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-arquitectura-de-software</x:v>
       </x:c>
     </x:row>
-    <x:row r="84">
-      <x:c r="A84" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B84" s="51" t="str">
+    <x:row r="340">
+      <x:c r="A340" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B340" s="110" t="str">
         <x:v>Maestría en Ingeniería de Datos e Infraestructura</x:v>
       </x:c>
-      <x:c r="C84" s="52" t="str">
+      <x:c r="C340" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-ingenieria-de-datos-e-infraestructura</x:v>
       </x:c>
     </x:row>
-    <x:row r="85">
-      <x:c r="A85" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B85" s="26" t="str">
+    <x:row r="341">
+      <x:c r="A341" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B341" s="73" t="str">
         <x:v>Maestría en Infraestructura y Cómputo en la Nube</x:v>
       </x:c>
-      <x:c r="C85" s="32" t="str">
+      <x:c r="C341" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-infraestructura-y-computo-en-la-nube</x:v>
       </x:c>
     </x:row>
-    <x:row r="86">
-      <x:c r="A86" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B86" s="51" t="str">
+    <x:row r="342">
+      <x:c r="A342" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B342" s="110" t="str">
         <x:v>Maestría en Interfaces Inteligentes y Tecnología Inmersiva</x:v>
       </x:c>
-      <x:c r="C86" s="52" t="str">
+      <x:c r="C342" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-interfaces-inteligentes-y-tecnologia-inmersiva</x:v>
       </x:c>
     </x:row>
-    <x:row r="87">
-      <x:c r="A87" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B87" s="26" t="str">
+    <x:row r="343">
+      <x:c r="A343" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B343" s="73" t="str">
         <x:v>Maestría en Gestión de la Calidad y Procesos Industriales</x:v>
       </x:c>
-      <x:c r="C87" s="32" t="str">
+      <x:c r="C343" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-gestion-de-la-calidad-y-procesos-industriales</x:v>
       </x:c>
     </x:row>
-    <x:row r="88">
-      <x:c r="A88" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B88" s="51" t="str">
+    <x:row r="344">
+      <x:c r="A344" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B344" s="110" t="str">
         <x:v>Maestría en Evaluación de Riesgos Tecnológicos y Resiliencia Operativa</x:v>
       </x:c>
-      <x:c r="C88" s="52" t="str">
+      <x:c r="C344" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-evaluacion-de-riesgos-tecnologicos-y-resiliencia-operativa</x:v>
       </x:c>
     </x:row>
-    <x:row r="89">
-      <x:c r="A89" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B89" s="26" t="str">
+    <x:row r="345">
+      <x:c r="A345" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B345" s="73" t="str">
         <x:v>Maestría en Gestión de Riesgos Ambientales</x:v>
       </x:c>
-      <x:c r="C89" s="32" t="str">
+      <x:c r="C345" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-gestion-de-riesgos-ambientales</x:v>
       </x:c>
     </x:row>
-    <x:row r="90">
-      <x:c r="A90" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B90" s="51" t="str">
+    <x:row r="346">
+      <x:c r="A346" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B346" s="110" t="str">
         <x:v>MBA Internacional</x:v>
       </x:c>
-      <x:c r="C90" s="52" t="str">
+      <x:c r="C346" s="111" t="str">
         <x:v>https://utel.edu.mx/mba-internacional</x:v>
       </x:c>
     </x:row>
-    <x:row r="91">
-      <x:c r="A91" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B91" s="26" t="str">
+    <x:row r="347">
+      <x:c r="A347" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B347" s="73" t="str">
         <x:v>Maestría en Administración de Negocios Deportivos</x:v>
       </x:c>
-      <x:c r="C91" s="32" t="str">
+      <x:c r="C347" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-administracion-de-negocios-deportivos</x:v>
       </x:c>
     </x:row>
-    <x:row r="92">
-      <x:c r="A92" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B92" s="51" t="str">
+    <x:row r="348">
+      <x:c r="A348" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B348" s="110" t="str">
         <x:v>Maestría en Mercadotecnia Digital y Comercio Electrónico</x:v>
       </x:c>
-      <x:c r="C92" s="52" t="str">
+      <x:c r="C348" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-mercadotecnia-digital-y-comercio-electronico</x:v>
       </x:c>
     </x:row>
-    <x:row r="93">
-      <x:c r="A93" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B93" s="26" t="str">
+    <x:row r="349">
+      <x:c r="A349" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B349" s="73" t="str">
         <x:v>Maestría en Administración de Recursos Humanos</x:v>
       </x:c>
-      <x:c r="C93" s="32" t="str">
+      <x:c r="C349" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-administracion-de-recursos-humanos</x:v>
       </x:c>
     </x:row>
-    <x:row r="94">
-      <x:c r="A94" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B94" s="51" t="str">
+    <x:row r="350">
+      <x:c r="A350" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B350" s="110" t="str">
         <x:v>Maestría en Administración de Tecnologías de la Información</x:v>
       </x:c>
-      <x:c r="C94" s="52" t="str">
+      <x:c r="C350" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-administracion-de-tecnologias-de-la-informacion</x:v>
       </x:c>
     </x:row>
-    <x:row r="95">
-      <x:c r="A95" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B95" s="26" t="str">
+    <x:row r="351">
+      <x:c r="A351" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B351" s="73" t="str">
         <x:v>Maestría en Dirección de Ventas</x:v>
       </x:c>
-      <x:c r="C95" s="32" t="str">
+      <x:c r="C351" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-direccion-de-ventas</x:v>
       </x:c>
     </x:row>
-    <x:row r="96">
-      <x:c r="A96" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B96" s="51" t="str">
+    <x:row r="352">
+      <x:c r="A352" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B352" s="110" t="str">
         <x:v>Maestría en Administración en Mercadotecnia Estratégica</x:v>
       </x:c>
-      <x:c r="C96" s="52" t="str">
+      <x:c r="C352" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-administracion-en-mercadotecnia-estrategica</x:v>
       </x:c>
     </x:row>
-    <x:row r="97">
-      <x:c r="A97" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B97" s="26" t="str">
+    <x:row r="353">
+      <x:c r="A353" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B353" s="73" t="str">
         <x:v>Maestría en Administración Pública</x:v>
       </x:c>
-      <x:c r="C97" s="32" t="str">
+      <x:c r="C353" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-administracion-publica</x:v>
       </x:c>
     </x:row>
-    <x:row r="98">
-      <x:c r="A98" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B98" s="51" t="str">
+    <x:row r="354">
+      <x:c r="A354" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B354" s="110" t="str">
         <x:v>Maestría en Coaching Integral y Organizacional</x:v>
       </x:c>
-      <x:c r="C98" s="52" t="str">
+      <x:c r="C354" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-coaching-integral-y-organizacional</x:v>
       </x:c>
     </x:row>
-    <x:row r="99">
-      <x:c r="A99" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B99" s="26" t="str">
+    <x:row r="355">
+      <x:c r="A355" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B355" s="73" t="str">
         <x:v>Maestría en Comercio Internacional</x:v>
       </x:c>
-      <x:c r="C99" s="32" t="str">
+      <x:c r="C355" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-comercio-internacional</x:v>
       </x:c>
     </x:row>
-    <x:row r="100">
-      <x:c r="A100" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B100" s="51" t="str">
+    <x:row r="356">
+      <x:c r="A356" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B356" s="110" t="str">
         <x:v>Maestría en Gestión Estratégica del Capital Humano</x:v>
       </x:c>
-      <x:c r="C100" s="52" t="str">
+      <x:c r="C356" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-gestion-estrategica-del-capital-humano</x:v>
       </x:c>
     </x:row>
-    <x:row r="101">
-      <x:c r="A101" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B101" s="26" t="str">
+    <x:row r="357">
+      <x:c r="A357" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B357" s="73" t="str">
         <x:v>Maestría en Gestión Organizacional Positiva</x:v>
       </x:c>
-      <x:c r="C101" s="32" t="str">
+      <x:c r="C357" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-gestion-organizacional-positiva</x:v>
       </x:c>
     </x:row>
-    <x:row r="102">
-      <x:c r="A102" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B102" s="51" t="str">
+    <x:row r="358">
+      <x:c r="A358" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B358" s="110" t="str">
         <x:v>Maestría en Finanzas</x:v>
       </x:c>
-      <x:c r="C102" s="52" t="str">
+      <x:c r="C358" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-finanzas</x:v>
       </x:c>
     </x:row>
-    <x:row r="103">
-      <x:c r="A103" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B103" s="26" t="str">
+    <x:row r="359">
+      <x:c r="A359" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B359" s="73" t="str">
         <x:v>Maestría en Administración Pública con CIFAL Málaga y UNITAR</x:v>
       </x:c>
-      <x:c r="C103" s="32" t="str">
+      <x:c r="C359" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-administracion-publica-con-cifal-malaga-y-unitar</x:v>
       </x:c>
     </x:row>
-    <x:row r="104">
-      <x:c r="A104" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B104" s="51" t="str">
+    <x:row r="360">
+      <x:c r="A360" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B360" s="110" t="str">
         <x:v>Maestría en Impuestos</x:v>
       </x:c>
-      <x:c r="C104" s="52" t="str">
+      <x:c r="C360" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-impuestos</x:v>
       </x:c>
     </x:row>
-    <x:row r="105">
-      <x:c r="A105" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B105" s="26" t="str">
+    <x:row r="361">
+      <x:c r="A361" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B361" s="73" t="str">
         <x:v>Maestría en Administración de Instituciones Educativas</x:v>
       </x:c>
-      <x:c r="C105" s="32" t="str">
+      <x:c r="C361" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-administracion-de-instituciones-educativas</x:v>
       </x:c>
     </x:row>
-    <x:row r="106">
-      <x:c r="A106" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B106" s="51" t="str">
+    <x:row r="362">
+      <x:c r="A362" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B362" s="110" t="str">
         <x:v>Maestría en Administración de Negocios</x:v>
       </x:c>
-      <x:c r="C106" s="52" t="str">
+      <x:c r="C362" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-administracion-de-negocios</x:v>
       </x:c>
     </x:row>
-    <x:row r="107">
-      <x:c r="A107" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B107" s="26" t="str">
+    <x:row r="363">
+      <x:c r="A363" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B363" s="73" t="str">
         <x:v>Maestría en Alta Dirección y Gobierno Corporativo</x:v>
       </x:c>
-      <x:c r="C107" s="32" t="str">
+      <x:c r="C363" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-alta-direccion-y-gobierno-corporativo</x:v>
       </x:c>
     </x:row>
-    <x:row r="108">
-      <x:c r="A108" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B108" s="51" t="str">
+    <x:row r="364">
+      <x:c r="A364" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B364" s="110" t="str">
         <x:v>Maestría en Dirección de Proyectos de Innovación</x:v>
       </x:c>
-      <x:c r="C108" s="52" t="str">
+      <x:c r="C364" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-direccion-de-proyectos-de-innovacion</x:v>
       </x:c>
     </x:row>
-    <x:row r="109">
-      <x:c r="A109" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B109" s="26" t="str">
+    <x:row r="365">
+      <x:c r="A365" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B365" s="73" t="str">
         <x:v>Maestría en Gestión Directiva de Instituciones en Salud</x:v>
       </x:c>
-      <x:c r="C109" s="32" t="str">
+      <x:c r="C365" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-gestion-directiva-de-instituciones-en-salud</x:v>
       </x:c>
     </x:row>
-    <x:row r="110">
-      <x:c r="A110" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B110" s="51" t="str">
+    <x:row r="366">
+      <x:c r="A366" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B366" s="110" t="str">
         <x:v>Maestría en Logística y Cadena de Suministro</x:v>
       </x:c>
-      <x:c r="C110" s="52" t="str">
+      <x:c r="C366" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-logistica-y-cadena-de-suministro</x:v>
       </x:c>
     </x:row>
-    <x:row r="111">
-      <x:c r="A111" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B111" s="26" t="str">
+    <x:row r="367">
+      <x:c r="A367" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B367" s="73" t="str">
         <x:v>Maestría en Asesoría Empresarial Estratégica</x:v>
       </x:c>
-      <x:c r="C111" s="32" t="str">
+      <x:c r="C367" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-asesoria-empresarial-estrategica</x:v>
       </x:c>
     </x:row>
-    <x:row r="112">
-      <x:c r="A112" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B112" s="51" t="str">
+    <x:row r="368">
+      <x:c r="A368" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B368" s="110" t="str">
         <x:v>Maestría en Inteligencia Financiera y Detección de Fraudes</x:v>
       </x:c>
-      <x:c r="C112" s="52" t="str">
+      <x:c r="C368" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-inteligencia-financiera-y-deteccion-de-fraudes</x:v>
       </x:c>
     </x:row>
-    <x:row r="113">
-      <x:c r="A113" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B113" s="26" t="str">
+    <x:row r="369">
+      <x:c r="A369" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B369" s="73" t="str">
         <x:v>Maestría en Administración de Riesgos Financieros</x:v>
       </x:c>
-      <x:c r="C113" s="32" t="str">
+      <x:c r="C369" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-administracion-de-riesgos-financieros</x:v>
       </x:c>
     </x:row>
-    <x:row r="114">
-      <x:c r="A114" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B114" s="51" t="str">
+    <x:row r="370">
+      <x:c r="A370" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B370" s="110" t="str">
         <x:v>Maestría en Innovación en Modelos de Negocio</x:v>
       </x:c>
-      <x:c r="C114" s="52" t="str">
+      <x:c r="C370" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-innovacion-en-modelos-de-negocio</x:v>
       </x:c>
     </x:row>
-    <x:row r="115">
-      <x:c r="A115" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B115" s="26" t="str">
+    <x:row r="371">
+      <x:c r="A371" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B371" s="73" t="str">
         <x:v>Maestría en Finanzas Sustentables y Proyectos de Inversión</x:v>
       </x:c>
-      <x:c r="C115" s="32" t="str">
+      <x:c r="C371" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-finanzas-sustentables-y-proyectos-de-inversion</x:v>
       </x:c>
     </x:row>
-    <x:row r="116">
-      <x:c r="A116" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B116" s="51" t="str">
+    <x:row r="372">
+      <x:c r="A372" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B372" s="110" t="str">
         <x:v>Maestría en Economía Digital y Nuevas Formas de Mercado</x:v>
       </x:c>
-      <x:c r="C116" s="52" t="str">
+      <x:c r="C372" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-economia-digital-y-nuevas-formas-de-mercado</x:v>
       </x:c>
     </x:row>
-    <x:row r="117">
-      <x:c r="A117" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B117" s="26" t="str">
+    <x:row r="373">
+      <x:c r="A373" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B373" s="73" t="str">
         <x:v>Maestría en Auditoría Financiera</x:v>
       </x:c>
-      <x:c r="C117" s="32" t="str">
+      <x:c r="C373" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-auditoria-financiera</x:v>
       </x:c>
     </x:row>
-    <x:row r="118">
-      <x:c r="A118" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B118" s="51" t="str">
+    <x:row r="374">
+      <x:c r="A374" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B374" s="110" t="str">
         <x:v>Maestría en Finanzas Públicas y Gestión Gubernamental</x:v>
       </x:c>
-      <x:c r="C118" s="52" t="str">
+      <x:c r="C374" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-finanzas-publicas-y-gestion-gubernamental</x:v>
       </x:c>
     </x:row>
-    <x:row r="119">
-      <x:c r="A119" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B119" s="26" t="str">
+    <x:row r="375">
+      <x:c r="A375" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B375" s="73" t="str">
         <x:v>Maestría en Economía Sustentable y Empresas Responsables</x:v>
       </x:c>
-      <x:c r="C119" s="32" t="str">
+      <x:c r="C375" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-economia-sustentable-y-empresas-responsables</x:v>
       </x:c>
     </x:row>
-    <x:row r="120">
-      <x:c r="A120" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B120" s="51" t="str">
+    <x:row r="376">
+      <x:c r="A376" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B376" s="110" t="str">
         <x:v>Maestría en Estrategias de Comercio Internacional y Aduanas</x:v>
       </x:c>
-      <x:c r="C120" s="52" t="str">
+      <x:c r="C376" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-estrategias-de-comercio-internacional-y-aduanas</x:v>
       </x:c>
     </x:row>
-    <x:row r="121">
-      <x:c r="A121" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B121" s="26" t="str">
+    <x:row r="377">
+      <x:c r="A377" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B377" s="73" t="str">
         <x:v>Maestría en Cultura y Transformación Digital</x:v>
       </x:c>
-      <x:c r="C121" s="32" t="str">
+      <x:c r="C377" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-cultura-y-transformacion-digital</x:v>
       </x:c>
     </x:row>
-    <x:row r="122">
-      <x:c r="A122" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B122" s="51" t="str">
+    <x:row r="378">
+      <x:c r="A378" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B378" s="110" t="str">
         <x:v>Maestría en Educación y Docencia</x:v>
       </x:c>
-      <x:c r="C122" s="52" t="str">
+      <x:c r="C378" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-educacion-y-docencia</x:v>
       </x:c>
     </x:row>
-    <x:row r="123">
-      <x:c r="A123" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B123" s="26" t="str">
+    <x:row r="379">
+      <x:c r="A379" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B379" s="73" t="str">
         <x:v>Maestría en Tecnología Educativa</x:v>
       </x:c>
-      <x:c r="C123" s="32" t="str">
+      <x:c r="C379" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-tecnologia-educativa</x:v>
       </x:c>
     </x:row>
-    <x:row r="124">
-      <x:c r="A124" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B124" s="51" t="str">
+    <x:row r="380">
+      <x:c r="A380" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B380" s="110" t="str">
         <x:v>Maestría en Desarrollo Sustentable y Gestión Ambiental</x:v>
       </x:c>
-      <x:c r="C124" s="52" t="str">
+      <x:c r="C380" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-desarrollo-sustentable-y-gestion-ambiental</x:v>
       </x:c>
     </x:row>
-    <x:row r="125">
-      <x:c r="A125" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B125" s="26" t="str">
+    <x:row r="381">
+      <x:c r="A381" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B381" s="73" t="str">
         <x:v>Maestría en Responsabilidad Social</x:v>
       </x:c>
-      <x:c r="C125" s="32" t="str">
+      <x:c r="C381" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-responsabilidad-social</x:v>
       </x:c>
     </x:row>
-    <x:row r="126">
-      <x:c r="A126" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B126" s="51" t="str">
+    <x:row r="382">
+      <x:c r="A382" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B382" s="110" t="str">
         <x:v>Maestría en Innovación Educativa y Diseño Instruccional</x:v>
       </x:c>
-      <x:c r="C126" s="52" t="str">
+      <x:c r="C382" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-innovacion-educativa-y-diseno-instruccional</x:v>
       </x:c>
     </x:row>
-    <x:row r="127">
-      <x:c r="A127" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B127" s="26" t="str">
+    <x:row r="383">
+      <x:c r="A383" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B383" s="73" t="str">
         <x:v>Maestría en Educación Inteligente y Diseño Instruccional con Inteligencia Artificial</x:v>
       </x:c>
-      <x:c r="C127" s="32" t="str">
+      <x:c r="C383" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-educacion-inteligente-y-dise%C3%B1o-institucional-con-inteligencia-artificial</x:v>
       </x:c>
     </x:row>
-    <x:row r="128">
-      <x:c r="A128" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B128" s="51" t="str">
+    <x:row r="384">
+      <x:c r="A384" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B384" s="110" t="str">
         <x:v>Maestría en Energías Renovables y Eficiencia Energética</x:v>
       </x:c>
-      <x:c r="C128" s="52" t="str">
+      <x:c r="C384" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-energias-renovables-y-eficiencia-energetica</x:v>
       </x:c>
     </x:row>
-    <x:row r="129">
-      <x:c r="A129" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B129" s="26" t="str">
+    <x:row r="385">
+      <x:c r="A385" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B385" s="73" t="str">
         <x:v>Maestría en Historia Pública y Educación Patrimonial</x:v>
       </x:c>
-      <x:c r="C129" s="32" t="str">
+      <x:c r="C385" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-historia-publica-y-educacion-patrimonial</x:v>
       </x:c>
     </x:row>
-    <x:row r="130">
-      <x:c r="A130" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B130" s="51" t="str">
+    <x:row r="386">
+      <x:c r="A386" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B386" s="110" t="str">
         <x:v>Maestría en Análisis Político y Opinión Pública</x:v>
       </x:c>
-      <x:c r="C130" s="52" t="str">
+      <x:c r="C386" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-analisis-politico-y-opinion-publica</x:v>
       </x:c>
     </x:row>
-    <x:row r="131">
-      <x:c r="A131" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B131" s="26" t="str">
+    <x:row r="387">
+      <x:c r="A387" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B387" s="73" t="str">
         <x:v>Maestría en Comunicación Social y Participación Ciudadana</x:v>
       </x:c>
-      <x:c r="C131" s="32" t="str">
+      <x:c r="C387" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-comunicacion-social-y-participacion-ciudadana</x:v>
       </x:c>
     </x:row>
-    <x:row r="132">
-      <x:c r="A132" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B132" s="51" t="str">
+    <x:row r="388">
+      <x:c r="A388" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B388" s="110" t="str">
         <x:v>Maestría en Políticas Sociales y Bienestar Social</x:v>
       </x:c>
-      <x:c r="C132" s="52" t="str">
+      <x:c r="C388" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-politicas-sociales-y-bienestar-social</x:v>
       </x:c>
     </x:row>
-    <x:row r="133">
-      <x:c r="A133" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B133" s="26" t="str">
+    <x:row r="389">
+      <x:c r="A389" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B389" s="73" t="str">
         <x:v>Maestría en Educación Inclusiva y Diversidad</x:v>
       </x:c>
-      <x:c r="C133" s="32" t="str">
+      <x:c r="C389" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-educacion-inclusiva-y-diversidad</x:v>
       </x:c>
     </x:row>
-    <x:row r="134">
-      <x:c r="A134" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B134" s="51" t="str">
+    <x:row r="390">
+      <x:c r="A390" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B390" s="110" t="str">
         <x:v>Maestría en Filosofía y Pensamiento Crítico</x:v>
       </x:c>
-      <x:c r="C134" s="52" t="str">
+      <x:c r="C390" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-filosofia-y-pensamiento-critico</x:v>
       </x:c>
     </x:row>
-    <x:row r="135">
-      <x:c r="A135" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B135" s="26" t="str">
+    <x:row r="391">
+      <x:c r="A391" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B391" s="73" t="str">
         <x:v>Maestría en Justicia Social y Transformación Comunitaria</x:v>
       </x:c>
-      <x:c r="C135" s="32" t="str">
+      <x:c r="C391" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-justicia-social-y-transformacion-comunitaria</x:v>
       </x:c>
     </x:row>
-    <x:row r="136">
-      <x:c r="A136" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B136" s="51" t="str">
+    <x:row r="392">
+      <x:c r="A392" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B392" s="110" t="str">
         <x:v>Maestría en Mindfulness (Conciencia Plena Aplicada)</x:v>
       </x:c>
-      <x:c r="C136" s="52" t="str">
+      <x:c r="C392" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-conciencia-plena-aplicada</x:v>
       </x:c>
     </x:row>
-    <x:row r="137">
-      <x:c r="A137" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B137" s="26" t="str">
+    <x:row r="393">
+      <x:c r="A393" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B393" s="73" t="str">
         <x:v>Maestría en Psicología Transpersonal</x:v>
       </x:c>
-      <x:c r="C137" s="32" t="str">
+      <x:c r="C393" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-psicologia-transpersonal</x:v>
       </x:c>
     </x:row>
-    <x:row r="138">
-      <x:c r="A138" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B138" s="51" t="str">
+    <x:row r="394">
+      <x:c r="A394" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B394" s="110" t="str">
         <x:v>Maestría en Dirección de Empresas Turísticas</x:v>
       </x:c>
-      <x:c r="C138" s="52" t="str">
+      <x:c r="C394" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-direccion-de-empresas-turisticas</x:v>
       </x:c>
     </x:row>
-    <x:row r="139">
-      <x:c r="A139" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B139" s="26" t="str">
+    <x:row r="395">
+      <x:c r="A395" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B395" s="73" t="str">
         <x:v>Maestría en Dirección de Negocios de Alimentos y Bebidas</x:v>
       </x:c>
-      <x:c r="C139" s="32" t="str">
+      <x:c r="C395" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-direccion-de-negocios-de-alimentos-y-bebidas</x:v>
       </x:c>
     </x:row>
-    <x:row r="140">
-      <x:c r="A140" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B140" s="51" t="str">
+    <x:row r="396">
+      <x:c r="A396" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B396" s="110" t="str">
         <x:v>Maestría en Turismo Digital y Gestión de Plataformas</x:v>
       </x:c>
-      <x:c r="C140" s="52" t="str">
+      <x:c r="C396" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-turismo-digital-y-gestion-de-plataformas</x:v>
       </x:c>
     </x:row>
-    <x:row r="141">
-      <x:c r="A141" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B141" s="26" t="str">
+    <x:row r="397">
+      <x:c r="A397" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B397" s="73" t="str">
         <x:v>Maestría en Dirección Estratégica de Hospitalidad y Bienestar</x:v>
       </x:c>
-      <x:c r="C141" s="32" t="str">
+      <x:c r="C397" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-direccion-estrategica-de-hospitalidad-y-bienestar</x:v>
       </x:c>
     </x:row>
-    <x:row r="142">
-      <x:c r="A142" s="50" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B142" s="51" t="str">
+    <x:row r="398">
+      <x:c r="A398" s="109" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B398" s="110" t="str">
         <x:v>Maestría en Organización de Eventos Corporativos y Convenciones</x:v>
       </x:c>
-      <x:c r="C142" s="52" t="str">
+      <x:c r="C398" s="111" t="str">
         <x:v>https://utel.edu.mx/maestria-en-organizacion-de-eventos-corporativos-y-convenciones</x:v>
       </x:c>
     </x:row>
-    <x:row r="143">
-      <x:c r="A143" s="31" t="str">
-        <x:v>Maestría</x:v>
-      </x:c>
-      <x:c r="B143" s="26" t="str">
+    <x:row r="399">
+      <x:c r="A399" s="97" t="str">
+        <x:v>Maestría Híbrida</x:v>
+      </x:c>
+      <x:c r="B399" s="73" t="str">
         <x:v>Maestría en Planeación Turística y Desarrollo Regional</x:v>
       </x:c>
-      <x:c r="C143" s="32" t="str">
+      <x:c r="C399" s="98" t="str">
         <x:v>https://utel.edu.mx/maestria-en-planeacion-turistica-y-desarrollo-regional</x:v>
       </x:c>
     </x:row>
-    <x:row r="144">
-      <x:c r="A144" s="50" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B144" s="51" t="str">
-        <x:v>Doctorado en Ciencia de Datos e Inteligencia Artificial</x:v>
-      </x:c>
-      <x:c r="C144" s="52" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-ciencia-de-datos-e-inteligencia-artificial</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145">
-      <x:c r="A145" s="31" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B145" s="26" t="str">
-        <x:v>Doctorado en Ciberseguridad de Sistemas Autónomos</x:v>
-      </x:c>
-      <x:c r="C145" s="32" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-ciberseguridad-de-sistemas-autonomos</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146">
-      <x:c r="A146" s="50" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B146" s="51" t="str">
-        <x:v>Doctorado en Ciberseguridad y Gestión de Riesgos Digitales</x:v>
-      </x:c>
-      <x:c r="C146" s="52" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-ciberseguridad-y-gestion-de-riesgos-digitales</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147">
-      <x:c r="A147" s="31" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B147" s="26" t="str">
-        <x:v>Doctorado en Administración Estratégica Empresarial</x:v>
-      </x:c>
-      <x:c r="C147" s="32" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-administracion-estrategica-empresarial</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148">
-      <x:c r="A148" s="50" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B148" s="51" t="str">
-        <x:v>Doctorado en Alta Dirección y Gobierno Corporativo</x:v>
-      </x:c>
-      <x:c r="C148" s="52" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-alta-direccion-y-gobierno-corporativo</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149">
-      <x:c r="A149" s="31" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B149" s="26" t="str">
-        <x:v>Doctorado en Gestión e Innovación Tecnológica</x:v>
-      </x:c>
-      <x:c r="C149" s="32" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-gestion-e-innovacion-tecnologica</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150">
-      <x:c r="A150" s="50" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B150" s="51" t="str">
-        <x:v>Doctorado en Educación</x:v>
-      </x:c>
-      <x:c r="C150" s="52" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-educacion</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151">
-      <x:c r="A151" s="31" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B151" s="26" t="str">
-        <x:v>Doctorado en Tecnología Educativa e Innovación Didáctica</x:v>
-      </x:c>
-      <x:c r="C151" s="32" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-tecnologia-educativa-e-innovacion-didactica</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152">
-      <x:c r="A152" s="50" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B152" s="51" t="str">
-        <x:v>Doctorado en Evaluación de Políticas Sociales y Programas Públicos</x:v>
-      </x:c>
-      <x:c r="C152" s="52" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-evaluacion-de-politicas-sociales-y-programas-publicos</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153">
-      <x:c r="A153" s="31" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B153" s="26" t="str">
-        <x:v>Doctorado en Políticas Públicas y Gobernanza</x:v>
-      </x:c>
-      <x:c r="C153" s="32" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-politicas-publicas-y-gobernanza</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154">
-      <x:c r="A154" s="50" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B154" s="51" t="str">
-        <x:v>Doctorado en Estudios Interculturales y Diversidad Humana</x:v>
-      </x:c>
-      <x:c r="C154" s="52" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-estudios-interculturales-y-diversidad-humana</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="31" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B155" s="26" t="str">
-        <x:v>Doctorado en Estudios Interdisciplinarios sobre América Latina</x:v>
-      </x:c>
-      <x:c r="C155" s="32" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-estudios-interdisciplinarios-sobre-america-latina</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156">
-      <x:c r="A156" s="50" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B156" s="51" t="str">
-        <x:v>Doctorado en Liderazgo Educativo y Gestión Escolar</x:v>
-      </x:c>
-      <x:c r="C156" s="52" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-liderazgo-educativo-y-gestion-escolar</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157">
-      <x:c r="A157" s="31" t="str">
-        <x:v>Doctorado</x:v>
-      </x:c>
-      <x:c r="B157" s="26" t="str">
-        <x:v>Doctorado en Desarrollo Humano</x:v>
-      </x:c>
-      <x:c r="C157" s="32" t="str">
-        <x:v>https://utel.edu.mx/doctorado-en-desarrollo-humano</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158">
-      <x:c r="A158" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B158" s="51" t="str">
-        <x:v>Diplomado en Project Management</x:v>
-      </x:c>
-      <x:c r="C158" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-project-management</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159">
-      <x:c r="A159" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B159" s="26" t="str">
-        <x:v>Diplomado en Ciencias de Datos e Inteligencia Artificial</x:v>
-      </x:c>
-      <x:c r="C159" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-ciencias-de-datos-e-inteligencia-artificial</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B160" s="51" t="str">
-        <x:v>Diplomado en Inteligencia Artificial Aplicada</x:v>
-      </x:c>
-      <x:c r="C160" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-inteligencia-artificial-aplicada</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161">
-      <x:c r="A161" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B161" s="26" t="str">
-        <x:v>Diplomado en Diseño y Desarrollo de Software</x:v>
-      </x:c>
-      <x:c r="C161" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-diseno-y-desarrollo-de-software</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162">
-      <x:c r="A162" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B162" s="51" t="str">
-        <x:v>Diplomado en Programación y Tecnología de Redes</x:v>
-      </x:c>
-      <x:c r="C162" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-programacion-y-tecnologia-de-redes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163">
-      <x:c r="A163" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B163" s="26" t="str">
-        <x:v>Diplomado en Gestión de Calidad y Mantenimiento de Software</x:v>
-      </x:c>
-      <x:c r="C163" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-gestion-de-calidad-y-mantenimiento-de-software</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164">
-      <x:c r="A164" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B164" s="51" t="str">
-        <x:v>Diplomado en Tecnologías de la Información Aplicadas a la Logística y el Transporte</x:v>
-      </x:c>
-      <x:c r="C164" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-tecnologias-de-la-informacion-aplicadas-a-la-logistica-y-el-transporte</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165">
-      <x:c r="A165" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B165" s="26" t="str">
-        <x:v>Diplomado en Estrategias y Operaciones de Transporte</x:v>
-      </x:c>
-      <x:c r="C165" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-estrategias-y-operaciones-de-transporte</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166">
-      <x:c r="A166" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B166" s="51" t="str">
-        <x:v>Diplomado en Animación Digital y Creación de Contenidos</x:v>
-      </x:c>
-      <x:c r="C166" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-animacion-digital-y-creacion-de-contenidos</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167">
-      <x:c r="A167" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B167" s="26" t="str">
-        <x:v>Diplomado en Desarrollo de Medios Interactivos</x:v>
-      </x:c>
-      <x:c r="C167" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-desarrollo-de-medios-interactivos</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168">
-      <x:c r="A168" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B168" s="51" t="str">
-        <x:v>Diplomado en Creatividad y Comunicación Digital</x:v>
-      </x:c>
-      <x:c r="C168" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-creatividad-y-comunicacion-digital</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169">
-      <x:c r="A169" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B169" s="26" t="str">
-        <x:v>Diplomado en Fuentes y Tecnología de Energías Sostenibles</x:v>
-      </x:c>
-      <x:c r="C169" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-fuentes-y-tecnologia-de-energias-sostenibles</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170">
-      <x:c r="A170" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B170" s="51" t="str">
-        <x:v>Diplomado en Gestión y Eficiencia de Sistemas Energéticos</x:v>
-      </x:c>
-      <x:c r="C170" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-gestion-y-eficiencia-de-sistemas-energeticos</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171">
-      <x:c r="A171" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B171" s="26" t="str">
-        <x:v>Diplomado en Transición Energética Sostenible</x:v>
-      </x:c>
-      <x:c r="C171" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-transicion-energetica-sostenible</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172">
-      <x:c r="A172" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B172" s="51" t="str">
-        <x:v>Diplomado en Principios en el Arte Digital y Animación</x:v>
-      </x:c>
-      <x:c r="C172" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-principios-en-el-arte-digital-y-animacion</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173">
-      <x:c r="A173" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B173" s="26" t="str">
-        <x:v>Diplomado en Desarrollo de E-learning</x:v>
-      </x:c>
-      <x:c r="C173" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-desarrollo-de-e-learning</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174">
-      <x:c r="A174" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B174" s="51" t="str">
-        <x:v>Diplomado en Administración de proyectos</x:v>
-      </x:c>
-      <x:c r="C174" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-administracion-de-proyectos</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175">
-      <x:c r="A175" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B175" s="26" t="str">
-        <x:v>Diplomado en Coaching Organizacional</x:v>
-      </x:c>
-      <x:c r="C175" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-coaching-organizacional</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176">
-      <x:c r="A176" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B176" s="51" t="str">
-        <x:v>Diplomado en Administración Financiera</x:v>
-      </x:c>
-      <x:c r="C176" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-administracion-financiera</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177">
-      <x:c r="A177" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B177" s="26" t="str">
-        <x:v>Diplomado en Dirección de Operaciones</x:v>
-      </x:c>
-      <x:c r="C177" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-direccion-de-operaciones</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178">
-      <x:c r="A178" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B178" s="51" t="str">
-        <x:v>Diplomado en Administración de Servicios de Salud</x:v>
-      </x:c>
-      <x:c r="C178" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-administracion-de-servicios-de-salud</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179">
-      <x:c r="A179" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B179" s="26" t="str">
-        <x:v>Diplomado en Contabilidad y Gestión Financiera</x:v>
-      </x:c>
-      <x:c r="C179" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-contabilidad-y-gestion-financiera</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180">
-      <x:c r="A180" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B180" s="51" t="str">
-        <x:v>Diplomado en Estrategia e Innovación de Negocios</x:v>
-      </x:c>
-      <x:c r="C180" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-estrategia-e-innovacion-de-negocios</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181">
-      <x:c r="A181" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B181" s="26" t="str">
-        <x:v>Diplomado en Análisis Económico Integral</x:v>
-      </x:c>
-      <x:c r="C181" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-analisis-Economico-integral</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182">
-      <x:c r="A182" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B182" s="51" t="str">
-        <x:v>Diplomado en Métodos Cuantitativos para la Toma de Decisiones</x:v>
-      </x:c>
-      <x:c r="C182" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-metodos-cuantitativos-para-la-toma-de-decisiones</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="183">
-      <x:c r="A183" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B183" s="26" t="str">
-        <x:v>Diplomado en Habilidades digitales para el ambiente laboral</x:v>
-      </x:c>
-      <x:c r="C183" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-habilidades-digitales-para-el-ambiente-laboral</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184">
-      <x:c r="A184" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B184" s="51" t="str">
-        <x:v>Diplomado en Pensamiento Crítico e Innovación</x:v>
-      </x:c>
-      <x:c r="C184" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-pensamiento-critico-e-innovacion</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="185">
-      <x:c r="A185" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B185" s="26" t="str">
-        <x:v>Diplomado en Soft skills y habilidades gerenciales</x:v>
-      </x:c>
-      <x:c r="C185" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-soft-skills-y-habilidades-gerenciales</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="186">
-      <x:c r="A186" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B186" s="51" t="str">
-        <x:v>Diplomado en Tanatología</x:v>
-      </x:c>
-      <x:c r="C186" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-tanatologia</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187">
-      <x:c r="A187" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B187" s="26" t="str">
-        <x:v>Diplomado en Diversidad y Equidad de género</x:v>
-      </x:c>
-      <x:c r="C187" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-diversidad-y-equidad-de-genero</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="188">
-      <x:c r="A188" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B188" s="51" t="str">
-        <x:v>Diplomado en Diseño y Evaluación en Entornos Digitales</x:v>
-      </x:c>
-      <x:c r="C188" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-diseno-y-evaluacion-en-Entornos-digitales</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189">
-      <x:c r="A189" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B189" s="26" t="str">
-        <x:v>Diplomado en Gestión de Experiencias de Aprendizaje en Ambientes Virtuales</x:v>
-      </x:c>
-      <x:c r="C189" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-gestion-de-experiencias-de-aprendizaje-en-ambientes-virtuales</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="190">
-      <x:c r="A190" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B190" s="51" t="str">
-        <x:v>Diplomado en Gestión Curricular en Educación a Distancia</x:v>
-      </x:c>
-      <x:c r="C190" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-gestion-curricular-en-educacion-a-distancia</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="191">
-      <x:c r="A191" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B191" s="26" t="str">
-        <x:v>Diplomado en Atención al Adulto Mayor</x:v>
-      </x:c>
-      <x:c r="C191" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-atencion-al-adulto-mayor</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="192">
-      <x:c r="A192" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B192" s="51" t="str">
-        <x:v>Diplomado en Nutrición Especial en Enfermedades Metabólicas</x:v>
-      </x:c>
-      <x:c r="C192" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-nutricion-especial-en-enfermedades-metabolicas</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="193">
-      <x:c r="A193" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B193" s="26" t="str">
-        <x:v>Diplomado en Rehabilitación del Adulto Mayor</x:v>
-      </x:c>
-      <x:c r="C193" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-rehabilitacion-del-adulto-mayor</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="194">
-      <x:c r="A194" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B194" s="51" t="str">
-        <x:v>Diplomado en Pruebas Psicológicas para Adultos</x:v>
-      </x:c>
-      <x:c r="C194" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-pruebas-psicologicas-para-adultos</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195">
-      <x:c r="A195" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B195" s="26" t="str">
-        <x:v>Diplomado en Mindfulness para los Individuos y las Familias</x:v>
-      </x:c>
-      <x:c r="C195" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-mindfulness-para-los-individuos-y-las-familias</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196">
-      <x:c r="A196" s="50" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B196" s="51" t="str">
-        <x:v>Diplomado en Educación en Ciencias de la Salud</x:v>
-      </x:c>
-      <x:c r="C196" s="52" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-educacion-en-ciencias-de-la-salud</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197">
-      <x:c r="A197" s="31" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B197" s="26" t="str">
-        <x:v>Diplomado en Actualización en Urgencias Médicas</x:v>
-      </x:c>
-      <x:c r="C197" s="32" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-actualizacion-en-urgencias-medicas</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198">
-      <x:c r="A198" s="56" t="str">
-        <x:v>Diplomado</x:v>
-      </x:c>
-      <x:c r="B198" s="57" t="str">
-        <x:v>Diplomado en Actualización en Gineco-Obstetricia para el Primer y Segundo Nivel de Atención</x:v>
-      </x:c>
-      <x:c r="C198" s="58" t="str">
-        <x:v>https://utel.edu.mx/diplomado-en-actualizacion-en-gineco-obstetricia-para-el-primer-y-segundo-nivel-de-atencion</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199">
-      <x:c r="A199" t="str">
-        <x:v>Bootcamp</x:v>
-      </x:c>
-      <x:c r="B199" t="str">
-        <x:v>Bootcamp Fundamentos de Python + Proyectos Ágiles con Scrum</x:v>
-      </x:c>
-      <x:c r="C199" t="str">
-        <x:v>https://utel.edu.mx/bootcamp-fundamentos-de-python-proyectos-agiles-con-scrum</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200">
-      <x:c r="A200" t="str">
-        <x:v>Bootcamp</x:v>
-      </x:c>
-      <x:c r="B200" t="str">
-        <x:v>Bootcamp Fundamentos de Ciencias de Datos + Proyectos Ágiles con Scrum</x:v>
-      </x:c>
-      <x:c r="C200" t="str">
-        <x:v>https://utel.edu.mx/bootcamp-fundamento-de-ciencias-de-datos-proyectos-agiles-con-scrum</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201">
-      <x:c r="A201" t="str">
-        <x:v>Bootcamp</x:v>
-      </x:c>
-      <x:c r="B201" t="str">
-        <x:v>Bootcamp Fundamentos de Desarrollo Web + Proyectos Ágiles con Scrum</x:v>
-      </x:c>
-      <x:c r="C201" t="str">
-        <x:v>https://utel.edu.mx/bootcamp-fundamentos-de-desarrollo-web-proyectos-agiles-con-scrum</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202">
-      <x:c r="A202" t="str">
-        <x:v>Bachillerato</x:v>
-      </x:c>
-      <x:c r="B202" t="str">
-        <x:v>Bachillerato General</x:v>
-      </x:c>
-      <x:c r="C202" t="str">
-        <x:v>https://utel.edu.mx/bachillerato</x:v>
+    <x:row r="400">
+      <x:c r="A400" s="109" t="str">
+        <x:v>Diplomado Presencial</x:v>
+      </x:c>
+      <x:c r="B400" s="110" t="str">
+        <x:v>Diplomado en Bienestar Integral y Coach en Nutrición</x:v>
+      </x:c>
+      <x:c r="C400" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-presencial-coach-nutricion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401">
+      <x:c r="A401" s="97" t="str">
+        <x:v>Diplomado Presencial</x:v>
+      </x:c>
+      <x:c r="B401" s="73" t="str">
+        <x:v>Diplomado en Consejería para la prevención del suicidio</x:v>
+      </x:c>
+      <x:c r="C401" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-presencial-consejero-prevencion-suicidio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402">
+      <x:c r="A402" s="109" t="str">
+        <x:v>Diplomado Presencial</x:v>
+      </x:c>
+      <x:c r="B402" s="110" t="str">
+        <x:v>Diplomado en Acompañamiento en Duelo y Pérdida</x:v>
+      </x:c>
+      <x:c r="C402" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-presencial-consejero-manejo-duelo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403">
+      <x:c r="A403" s="97" t="str">
+        <x:v>Diplomado Presencial</x:v>
+      </x:c>
+      <x:c r="B403" s="73" t="str">
+        <x:v>Diplomado en Influencer Marketing y Estrategia de Marca</x:v>
+      </x:c>
+      <x:c r="C403" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-presencial-estratega-marketing-influencers</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404">
+      <x:c r="A404" s="109" t="str">
+        <x:v>Diplomado Presencial</x:v>
+      </x:c>
+      <x:c r="B404" s="110" t="str">
+        <x:v>Diplomado en Gamificación y Estrategias Lúdicas para el Aprendizaje</x:v>
+      </x:c>
+      <x:c r="C404" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-presencial-estratega-ludico-aprendizaje</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405">
+      <x:c r="A405" s="97" t="str">
+        <x:v>Diplomado Presencial</x:v>
+      </x:c>
+      <x:c r="B405" s="73" t="str">
+        <x:v>Diplomado en IA, herramientas, datos y liderazgo digital</x:v>
+      </x:c>
+      <x:c r="C405" s="98" t="str">
+        <x:v>https://utel.edu.mx/diplomado-presencial-facilitador-ia-tech-mindset</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406">
+      <x:c r="A406" s="109" t="str">
+        <x:v>Diplomado Presencial</x:v>
+      </x:c>
+      <x:c r="B406" s="110" t="str">
+        <x:v>Diplomado en Cuidados Paliativos y Humanización en Salud</x:v>
+      </x:c>
+      <x:c r="C406" s="111" t="str">
+        <x:v>https://utel.edu.mx/diplomado-presencial-instructor-cuidados-paliativos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407">
+      <x:c r="A407" s="103" t="str">
+        <x:v>Diplomado Presencial</x:v>
+      </x:c>
+      <x:c r="B407" s="104" t="str">
+        <x:v>Diplomado en Mindfulness para entornos organizacionales</x:v>
+      </x:c>
+      <x:c r="C407" s="105" t="str">
+        <x:v>https://utel.edu.mx/diplomado-presencial-instructor-tecnicas-mindfulness</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8baa7c2abab24ce4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R066fe873a8724176"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3545,7 +6027,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3ad489155c8486e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R524eb811fdb449e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4123,7 +6605,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d5c65466f144dfd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27debda1366b4de1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4811,7 +7293,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a21d50d26164cdb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7a2c9014d5843d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4993,7 +7475,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57fd57160b37486d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbac19b1ba344b24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5175,7 +7657,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc54d273ae9754e53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61c93a4985644184"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5764,7 +8246,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90fd514441174b1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8745b3676e741cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6551,7 +9033,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb90d194695164906"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d518fffe6f3494d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8605,7 +11087,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd392a58bc314e50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79d7f108e32a4db2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10569,7 +13051,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1f5d1b5deca417d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72844ed6d021498d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12254,7 +14736,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfea8bdfef343402a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b4dadf1656a4647"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13444,7 +15926,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59ee5a0e19c44352"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8a82eb718ad4bac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14038,7 +16520,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20d3683baad043d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5aff260254347da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14627,7 +17109,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re47521aa312e46d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R727f044b946149a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15857,7 +18339,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38664ed9076d4603"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7a3ae0d5266492c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/backend/data/Programas_UTEL_Todos_los_Paises.xlsx
+++ b/backend/data/Programas_UTEL_Todos_los_Paises.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="México" sheetId="1" r:id="Rab219a6509d24c97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Argentina" sheetId="2" r:id="Red616b0de2a6495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colombia" sheetId="3" r:id="R23087300d3524154"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perú" sheetId="4" r:id="Re75c73e4d40b4cf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ecuador" sheetId="5" r:id="R962a1485113644e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USA" sheetId="6" r:id="R401749cd67ff4d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolivia" sheetId="7" r:id="R801c1c783ed04e56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chile" sheetId="8" r:id="R0f130f586d9640fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rep. Dominicana" sheetId="9" r:id="R3c44cf035e344e91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guatemala" sheetId="10" r:id="R4492c4cd422d4573"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panamá" sheetId="11" r:id="R262bb3361dd3410f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="El Salvador" sheetId="12" r:id="Rc9291afbe741490a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Philippines" sheetId="13" r:id="R72dcbcf7842b4926"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indonesia" sheetId="14" r:id="Rbec1ca992f5a4a9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paraguay" sheetId="15" r:id="Rc67221567fe349bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="México" sheetId="1" r:id="Rded5deab0b20458c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Argentina" sheetId="2" r:id="Rdb3423d586694d99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colombia" sheetId="3" r:id="R5042ba6aca334954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perú" sheetId="4" r:id="R2461a00554ac4e20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ecuador" sheetId="5" r:id="R673ef71e4f624036"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USA" sheetId="6" r:id="Rb34ffccb57294fab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolivia" sheetId="7" r:id="R2222c3979f17489e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chile" sheetId="8" r:id="Rb2b78b9a374840f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rep. Dominicana" sheetId="9" r:id="R403f9ceaec124ccf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guatemala" sheetId="10" r:id="Racecad5230ff40dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panamá" sheetId="11" r:id="R1e04af048ee24241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="El Salvador" sheetId="12" r:id="R86ccfec85ffa495b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Philippines" sheetId="13" r:id="R6531e83271104c49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indonesia" sheetId="14" r:id="R1d2443bfec874463"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paraguay" sheetId="15" r:id="R24ef9bf3851a408a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -113,54 +113,19 @@
     <x:border/>
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2206,7 +2171,7 @@
         <x:v>Bachillerato en línea</x:v>
       </x:c>
       <x:c r="B124" s="110" t="str">
-        <x:v>Bachillerato General</x:v>
+        <x:v>Bachillerato en línea</x:v>
       </x:c>
       <x:c r="C124" s="111" t="str">
         <x:v>https://utel.edu.mx/bachillerato</x:v>
@@ -5328,7 +5293,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R066fe873a8724176"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43696a243d684a93"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6027,7 +5992,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R524eb811fdb449e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc814b87bf5c24738"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6605,7 +6570,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27debda1366b4de1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d8f0b5a85c5428f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7293,7 +7258,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7a2c9014d5843d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b4165d3668e4c63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7475,7 +7440,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbac19b1ba344b24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R215632995c0a4e51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7657,7 +7622,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61c93a4985644184"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49766e6aa7da4c9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8246,7 +8211,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8745b3676e741cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15177e0ebc9f4719"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9033,7 +8998,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d518fffe6f3494d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77f85df2d6114399"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11087,7 +11052,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79d7f108e32a4db2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdeb9ad0e7ff84d0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13051,7 +13016,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72844ed6d021498d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c97e15699074d9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14736,7 +14701,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b4dadf1656a4647"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ab645aad06d424f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15926,7 +15891,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8a82eb718ad4bac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R675b081a39b54082"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16520,7 +16485,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5aff260254347da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01c84190db644453"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17109,7 +17074,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R727f044b946149a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fda5aa72501436d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18339,7 +18304,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7a3ae0d5266492c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff00ee03e2524906"/>
   </x:tableParts>
 </x:worksheet>
 </file>